--- a/HNG_2/HNG.xlsx
+++ b/HNG_2/HNG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VoDacHo\Gastric\HNG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XN\du-an-dung-chung\HNG_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD2AF34-E64F-48AF-A4A5-BE28ED14847D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306DE8C9-A642-45DB-969A-A479D5948056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$V$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$O$195</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1525,7 +1524,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -1848,7 +1847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2015,11 +2014,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2028,7 +2027,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2053,7 +2052,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2134,41 +2133,19 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2178,7 +2155,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2241,6 +2218,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2276,36 +2263,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2656,7 +2613,7 @@
       <c r="N1" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="O1" s="118" t="s">
+      <c r="O1" s="110" t="s">
         <v>491</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -2718,7 +2675,7 @@
       <c r="N2" s="2">
         <v>0.32500000000000001</v>
       </c>
-      <c r="O2" s="117">
+      <c r="O2" s="109">
         <v>4.875</v>
       </c>
       <c r="P2" s="2">
@@ -2780,7 +2737,7 @@
       <c r="N3" s="2">
         <v>0.25800000000000001</v>
       </c>
-      <c r="O3" s="117">
+      <c r="O3" s="109">
         <v>3.87</v>
       </c>
       <c r="P3" s="2">
@@ -2842,7 +2799,7 @@
       <c r="N4" s="2">
         <v>0.153</v>
       </c>
-      <c r="O4" s="117">
+      <c r="O4" s="109">
         <v>2.2949999999999999</v>
       </c>
       <c r="P4" s="2">
@@ -2904,7 +2861,7 @@
       <c r="N5" s="2">
         <v>0.33700000000000002</v>
       </c>
-      <c r="O5" s="117">
+      <c r="O5" s="109">
         <v>5.0550000000000006</v>
       </c>
       <c r="P5" s="2">
@@ -2966,7 +2923,7 @@
       <c r="N6" s="2">
         <v>0.498</v>
       </c>
-      <c r="O6" s="117">
+      <c r="O6" s="109">
         <v>9.9599999999999991</v>
       </c>
       <c r="P6" s="2">
@@ -3028,7 +2985,7 @@
       <c r="N7" s="2">
         <v>0.88200000000000001</v>
       </c>
-      <c r="O7" s="117">
+      <c r="O7" s="109">
         <v>13.23</v>
       </c>
       <c r="P7" s="2">
@@ -3090,7 +3047,7 @@
       <c r="N8" s="2">
         <v>0.64500000000000002</v>
       </c>
-      <c r="O8" s="117">
+      <c r="O8" s="109">
         <v>9.6750000000000007</v>
       </c>
       <c r="P8" s="2">
@@ -3152,7 +3109,7 @@
       <c r="N9" s="2">
         <v>0.49</v>
       </c>
-      <c r="O9" s="117">
+      <c r="O9" s="109">
         <v>7.35</v>
       </c>
       <c r="P9" s="2">
@@ -3214,7 +3171,7 @@
       <c r="N10" s="2">
         <v>0.46899999999999997</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="109">
         <v>7.8166666666666655</v>
       </c>
       <c r="P10" s="2">
@@ -3276,7 +3233,7 @@
       <c r="N11" s="2">
         <v>0.26300000000000001</v>
       </c>
-      <c r="O11" s="117">
+      <c r="O11" s="109">
         <v>3.9450000000000003</v>
       </c>
       <c r="P11" s="2">
@@ -3338,7 +3295,7 @@
       <c r="N12" s="2">
         <v>0.49099999999999999</v>
       </c>
-      <c r="O12" s="117">
+      <c r="O12" s="109">
         <v>8.1833333333333336</v>
       </c>
       <c r="P12" s="2">
@@ -3400,7 +3357,7 @@
       <c r="N13" s="2">
         <v>0.39</v>
       </c>
-      <c r="O13" s="117">
+      <c r="O13" s="109">
         <v>7.8000000000000007</v>
       </c>
       <c r="P13" s="2">
@@ -3462,7 +3419,7 @@
       <c r="N14" s="2">
         <v>0.36399999999999999</v>
       </c>
-      <c r="O14" s="117">
+      <c r="O14" s="109">
         <v>5.46</v>
       </c>
       <c r="P14" s="2">
@@ -3524,7 +3481,7 @@
       <c r="N15" s="2">
         <v>0.40200000000000002</v>
       </c>
-      <c r="O15" s="117">
+      <c r="O15" s="109">
         <v>6.03</v>
       </c>
       <c r="P15" s="2">
@@ -3586,7 +3543,7 @@
       <c r="N16" s="2">
         <v>0.57199999999999995</v>
       </c>
-      <c r="O16" s="117">
+      <c r="O16" s="109">
         <v>8.58</v>
       </c>
       <c r="P16" s="2">
@@ -3648,7 +3605,7 @@
       <c r="N17" s="2">
         <v>0.79800000000000004</v>
       </c>
-      <c r="O17" s="117">
+      <c r="O17" s="109">
         <v>13.3</v>
       </c>
       <c r="P17" s="2">
@@ -3710,7 +3667,7 @@
       <c r="N18" s="2">
         <v>0.38800000000000001</v>
       </c>
-      <c r="O18" s="117">
+      <c r="O18" s="109">
         <v>6.8470588235294123</v>
       </c>
       <c r="P18" s="2">
@@ -3772,7 +3729,7 @@
       <c r="N19" s="2">
         <v>0.875</v>
       </c>
-      <c r="O19" s="117">
+      <c r="O19" s="109">
         <v>15.441176470588236</v>
       </c>
       <c r="P19" s="2">
@@ -3834,7 +3791,7 @@
       <c r="N20" s="2">
         <v>0.57199999999999995</v>
       </c>
-      <c r="O20" s="117">
+      <c r="O20" s="109">
         <v>8.58</v>
       </c>
       <c r="P20" s="2">
@@ -3896,7 +3853,7 @@
       <c r="N21" s="2">
         <v>0.311</v>
       </c>
-      <c r="O21" s="117">
+      <c r="O21" s="109">
         <v>4.9105263157894736</v>
       </c>
       <c r="P21" s="2">
@@ -3958,7 +3915,7 @@
       <c r="N22" s="2">
         <v>0.40799999999999997</v>
       </c>
-      <c r="O22" s="117">
+      <c r="O22" s="109">
         <v>6.4421052631578943</v>
       </c>
       <c r="P22" s="2">
@@ -4020,7 +3977,7 @@
       <c r="N23" s="2">
         <v>0.46200000000000002</v>
       </c>
-      <c r="O23" s="117">
+      <c r="O23" s="109">
         <v>6.9300000000000006</v>
       </c>
       <c r="P23" s="2">
@@ -4082,7 +4039,7 @@
       <c r="N24" s="2">
         <v>0.42299999999999999</v>
       </c>
-      <c r="O24" s="117">
+      <c r="O24" s="109">
         <v>6.3449999999999998</v>
       </c>
       <c r="P24" s="2">
@@ -4144,7 +4101,7 @@
       <c r="N25" s="2">
         <v>0.73399999999999999</v>
       </c>
-      <c r="O25" s="117">
+      <c r="O25" s="109">
         <v>11.01</v>
       </c>
       <c r="P25" s="2">
@@ -4206,7 +4163,7 @@
       <c r="N26" s="2">
         <v>0.29399999999999998</v>
       </c>
-      <c r="O26" s="117">
+      <c r="O26" s="109">
         <v>4.6421052631578954</v>
       </c>
       <c r="P26" s="2">
@@ -4268,7 +4225,7 @@
       <c r="N27" s="2">
         <v>0.33100000000000002</v>
       </c>
-      <c r="O27" s="117">
+      <c r="O27" s="109">
         <v>6.62</v>
       </c>
       <c r="P27" s="2">
@@ -4330,7 +4287,7 @@
       <c r="N28" s="2">
         <v>0.51200000000000001</v>
       </c>
-      <c r="O28" s="117">
+      <c r="O28" s="109">
         <v>7.68</v>
       </c>
       <c r="P28" s="2">
@@ -4392,7 +4349,7 @@
       <c r="N29" s="2">
         <v>0.47299999999999998</v>
       </c>
-      <c r="O29" s="117">
+      <c r="O29" s="109">
         <v>9.4599999999999991</v>
       </c>
       <c r="P29" s="2">
@@ -4454,7 +4411,7 @@
       <c r="N30" s="2">
         <v>0.32300000000000001</v>
       </c>
-      <c r="O30" s="117">
+      <c r="O30" s="109">
         <v>6.46</v>
       </c>
       <c r="P30" s="2">
@@ -4516,7 +4473,7 @@
       <c r="N31" s="2">
         <v>1.1100000000000001</v>
       </c>
-      <c r="O31" s="117">
+      <c r="O31" s="109">
         <v>19.588235294117649</v>
       </c>
       <c r="P31" s="2">
@@ -4578,7 +4535,7 @@
       <c r="N32" s="2">
         <v>0.40400000000000003</v>
       </c>
-      <c r="O32" s="117">
+      <c r="O32" s="109">
         <v>6.7333333333333334</v>
       </c>
       <c r="P32" s="2">
@@ -4640,7 +4597,7 @@
       <c r="N33" s="2">
         <v>0.57199999999999995</v>
       </c>
-      <c r="O33" s="117">
+      <c r="O33" s="109">
         <v>10.094117647058823</v>
       </c>
       <c r="P33" s="2">
@@ -4702,7 +4659,7 @@
       <c r="N34" s="2">
         <v>0.247</v>
       </c>
-      <c r="O34" s="117">
+      <c r="O34" s="109">
         <v>4.3588235294117652</v>
       </c>
       <c r="P34" s="2">
@@ -4764,7 +4721,7 @@
       <c r="N35" s="2">
         <v>0.56899999999999995</v>
       </c>
-      <c r="O35" s="117">
+      <c r="O35" s="109">
         <v>11.38</v>
       </c>
       <c r="P35" s="2">
@@ -4826,7 +4783,7 @@
       <c r="N36" s="2">
         <v>0.44500000000000001</v>
       </c>
-      <c r="O36" s="117">
+      <c r="O36" s="109">
         <v>6.6749999999999998</v>
       </c>
       <c r="P36" s="2">
@@ -4888,7 +4845,7 @@
       <c r="N37" s="2">
         <v>0.21099999999999999</v>
       </c>
-      <c r="O37" s="117">
+      <c r="O37" s="109">
         <v>3.165</v>
       </c>
       <c r="P37" s="2">
@@ -4950,7 +4907,7 @@
       <c r="N38" s="2">
         <v>0.56599999999999995</v>
       </c>
-      <c r="O38" s="117">
+      <c r="O38" s="109">
         <v>8.4899999999999984</v>
       </c>
       <c r="P38" s="2">
@@ -5012,7 +4969,7 @@
       <c r="N39" s="2">
         <v>0.249</v>
       </c>
-      <c r="O39" s="117">
+      <c r="O39" s="109">
         <v>3.7349999999999999</v>
       </c>
       <c r="P39" s="2">
@@ -5074,7 +5031,7 @@
       <c r="N40" s="2">
         <v>0.30199999999999999</v>
       </c>
-      <c r="O40" s="117">
+      <c r="O40" s="109">
         <v>6.04</v>
       </c>
       <c r="P40" s="2">
@@ -5136,7 +5093,7 @@
       <c r="N41" s="2">
         <v>0.32200000000000001</v>
       </c>
-      <c r="O41" s="117">
+      <c r="O41" s="109">
         <v>6.44</v>
       </c>
       <c r="P41" s="2">
@@ -5198,7 +5155,7 @@
       <c r="N42" s="2">
         <v>0.21</v>
       </c>
-      <c r="O42" s="117">
+      <c r="O42" s="109">
         <v>3.15</v>
       </c>
       <c r="P42" s="2">
@@ -5260,7 +5217,7 @@
       <c r="N43" s="2">
         <v>0.33400000000000002</v>
       </c>
-      <c r="O43" s="117">
+      <c r="O43" s="109">
         <v>5.5666666666666673</v>
       </c>
       <c r="P43" s="2">
@@ -5322,7 +5279,7 @@
       <c r="N44" s="2">
         <v>0.60699999999999998</v>
       </c>
-      <c r="O44" s="117">
+      <c r="O44" s="109">
         <v>9.1050000000000004</v>
       </c>
       <c r="P44" s="2">
@@ -5384,7 +5341,7 @@
       <c r="N45" s="2">
         <v>0.42299999999999999</v>
       </c>
-      <c r="O45" s="117">
+      <c r="O45" s="109">
         <v>6.3449999999999998</v>
       </c>
       <c r="P45" s="2">
@@ -5446,7 +5403,7 @@
       <c r="N46" s="2">
         <v>0.32900000000000001</v>
       </c>
-      <c r="O46" s="117">
+      <c r="O46" s="109">
         <v>4.9350000000000005</v>
       </c>
       <c r="P46" s="2">
@@ -5508,7 +5465,7 @@
       <c r="N47" s="2">
         <v>0.40500000000000003</v>
       </c>
-      <c r="O47" s="117">
+      <c r="O47" s="109">
         <v>8.1</v>
       </c>
       <c r="P47" s="2">
@@ -5570,7 +5527,7 @@
       <c r="N48" s="2">
         <v>0.57499999999999996</v>
       </c>
-      <c r="O48" s="117">
+      <c r="O48" s="109">
         <v>9.0789473684210531</v>
       </c>
       <c r="P48" s="2">
@@ -5632,7 +5589,7 @@
       <c r="N49" s="2">
         <v>0.48</v>
       </c>
-      <c r="O49" s="117">
+      <c r="O49" s="109">
         <v>7.1999999999999993</v>
       </c>
       <c r="P49" s="2">
@@ -5694,7 +5651,7 @@
       <c r="N50" s="2">
         <v>0.747</v>
       </c>
-      <c r="O50" s="117">
+      <c r="O50" s="109">
         <v>11.205</v>
       </c>
       <c r="P50" s="2">
@@ -5756,7 +5713,7 @@
       <c r="N51" s="2">
         <v>0.379</v>
       </c>
-      <c r="O51" s="117">
+      <c r="O51" s="109">
         <v>5.6850000000000005</v>
       </c>
       <c r="P51" s="2">
@@ -5818,7 +5775,7 @@
       <c r="N52" s="2">
         <v>0.20300000000000001</v>
       </c>
-      <c r="O52" s="117">
+      <c r="O52" s="109">
         <v>3.0450000000000004</v>
       </c>
       <c r="P52" s="2">
@@ -5880,7 +5837,7 @@
       <c r="N53" s="2">
         <v>0.27400000000000002</v>
       </c>
-      <c r="O53" s="117">
+      <c r="O53" s="109">
         <v>5.48</v>
       </c>
       <c r="P53" s="2">
@@ -5942,7 +5899,7 @@
       <c r="N54" s="2">
         <v>0.39300000000000002</v>
       </c>
-      <c r="O54" s="117">
+      <c r="O54" s="109">
         <v>5.8950000000000005</v>
       </c>
       <c r="P54" s="2">
@@ -6004,7 +5961,7 @@
       <c r="N55" s="2">
         <v>0.29799999999999999</v>
       </c>
-      <c r="O55" s="117">
+      <c r="O55" s="109">
         <v>5.5874999999999995</v>
       </c>
       <c r="P55" s="2">
@@ -6066,7 +6023,7 @@
       <c r="N56" s="2">
         <v>0.77600000000000002</v>
       </c>
-      <c r="O56" s="117">
+      <c r="O56" s="109">
         <v>13.694117647058825</v>
       </c>
       <c r="P56" s="2">
@@ -6128,7 +6085,7 @@
       <c r="N57" s="2">
         <v>0.77800000000000002</v>
       </c>
-      <c r="O57" s="117">
+      <c r="O57" s="109">
         <v>13.729411764705883</v>
       </c>
       <c r="P57" s="2">
@@ -6190,7 +6147,7 @@
       <c r="N58" s="2">
         <v>0.72899999999999998</v>
       </c>
-      <c r="O58" s="117">
+      <c r="O58" s="109">
         <v>13.668749999999999</v>
       </c>
       <c r="P58" s="2">
@@ -6252,7 +6209,7 @@
       <c r="N59" s="2">
         <v>0.25</v>
       </c>
-      <c r="O59" s="117">
+      <c r="O59" s="109">
         <v>4.6875</v>
       </c>
       <c r="P59" s="2">
@@ -6314,7 +6271,7 @@
       <c r="N60" s="2">
         <v>0.89200000000000002</v>
       </c>
-      <c r="O60" s="117">
+      <c r="O60" s="109">
         <v>13.38</v>
       </c>
       <c r="P60" s="2">
@@ -6376,7 +6333,7 @@
       <c r="N61" s="2">
         <v>0.57699999999999996</v>
       </c>
-      <c r="O61" s="117">
+      <c r="O61" s="109">
         <v>8.6549999999999994</v>
       </c>
       <c r="P61" s="2">
@@ -6438,7 +6395,7 @@
       <c r="N62" s="2">
         <v>0.24399999999999999</v>
       </c>
-      <c r="O62" s="117">
+      <c r="O62" s="109">
         <v>4.0666666666666664</v>
       </c>
       <c r="P62" s="2">
@@ -6500,7 +6457,7 @@
       <c r="N63" s="2">
         <v>0.85499999999999998</v>
       </c>
-      <c r="O63" s="117">
+      <c r="O63" s="109">
         <v>17.099999999999998</v>
       </c>
       <c r="P63" s="2">
@@ -6562,7 +6519,7 @@
       <c r="N64" s="2">
         <v>0.67</v>
       </c>
-      <c r="O64" s="117">
+      <c r="O64" s="109">
         <v>10.050000000000001</v>
       </c>
       <c r="P64" s="2">
@@ -6624,7 +6581,7 @@
       <c r="N65" s="2">
         <v>0.495</v>
       </c>
-      <c r="O65" s="117">
+      <c r="O65" s="109">
         <v>9.28125</v>
       </c>
       <c r="P65" s="2">
@@ -6686,7 +6643,7 @@
       <c r="N66" s="2">
         <v>0.44600000000000001</v>
       </c>
-      <c r="O66" s="117">
+      <c r="O66" s="109">
         <v>7.4333333333333336</v>
       </c>
       <c r="P66" s="2">
@@ -6748,7 +6705,7 @@
       <c r="N67" s="2">
         <v>0.36</v>
       </c>
-      <c r="O67" s="117">
+      <c r="O67" s="109">
         <v>5.3999999999999995</v>
       </c>
       <c r="P67" s="2">
@@ -6810,7 +6767,7 @@
       <c r="N68" s="2">
         <v>0.32500000000000001</v>
       </c>
-      <c r="O68" s="117">
+      <c r="O68" s="109">
         <v>4.875</v>
       </c>
       <c r="P68" s="2">
@@ -6872,7 +6829,7 @@
       <c r="N69" s="2">
         <v>1</v>
       </c>
-      <c r="O69" s="117">
+      <c r="O69" s="109">
         <v>15</v>
       </c>
       <c r="P69" s="2">
@@ -6934,7 +6891,7 @@
       <c r="N70" s="2">
         <v>0.33</v>
       </c>
-      <c r="O70" s="117">
+      <c r="O70" s="109">
         <v>6.6000000000000005</v>
       </c>
       <c r="P70" s="2">
@@ -6996,7 +6953,7 @@
       <c r="N71" s="2">
         <v>0.55600000000000005</v>
       </c>
-      <c r="O71" s="117">
+      <c r="O71" s="109">
         <v>8.7789473684210524</v>
       </c>
       <c r="P71" s="2">
@@ -7058,7 +7015,7 @@
       <c r="N72" s="2">
         <v>0.28599999999999998</v>
       </c>
-      <c r="O72" s="117">
+      <c r="O72" s="109">
         <v>5.72</v>
       </c>
       <c r="P72" s="2">
@@ -7120,7 +7077,7 @@
       <c r="N73" s="2">
         <v>3.05</v>
       </c>
-      <c r="O73" s="117">
+      <c r="O73" s="109">
         <v>50.833333333333329</v>
       </c>
       <c r="P73" s="2">
@@ -7182,7 +7139,7 @@
       <c r="N74" s="2">
         <v>0.873</v>
       </c>
-      <c r="O74" s="117">
+      <c r="O74" s="109">
         <v>13.095000000000001</v>
       </c>
       <c r="P74" s="2">
@@ -7244,7 +7201,7 @@
       <c r="N75" s="2">
         <v>0.46400000000000002</v>
       </c>
-      <c r="O75" s="117">
+      <c r="O75" s="109">
         <v>8.1882352941176464</v>
       </c>
       <c r="P75" s="2">
@@ -7306,7 +7263,7 @@
       <c r="N76" s="2">
         <v>0.58699999999999997</v>
       </c>
-      <c r="O76" s="117">
+      <c r="O76" s="109">
         <v>8.8049999999999997</v>
       </c>
       <c r="P76" s="2">
@@ -7374,7 +7331,7 @@
       <c r="N77" s="2">
         <v>0.192</v>
       </c>
-      <c r="O77" s="117">
+      <c r="O77" s="109">
         <v>5.76</v>
       </c>
       <c r="P77" s="2">
@@ -7442,7 +7399,7 @@
       <c r="N78" s="2">
         <v>0.53100000000000003</v>
       </c>
-      <c r="O78" s="117">
+      <c r="O78" s="109">
         <v>15.930000000000001</v>
       </c>
       <c r="P78" s="2">
@@ -7510,7 +7467,7 @@
       <c r="N79" s="2">
         <v>0.23899999999999999</v>
       </c>
-      <c r="O79" s="117">
+      <c r="O79" s="109">
         <v>7.17</v>
       </c>
       <c r="P79" s="2">
@@ -7578,7 +7535,7 @@
       <c r="N80" s="2">
         <v>0.33200000000000002</v>
       </c>
-      <c r="O80" s="117">
+      <c r="O80" s="109">
         <v>9.9600000000000009</v>
       </c>
       <c r="P80" s="2">
@@ -7646,7 +7603,7 @@
       <c r="N81" s="2">
         <v>0.14499999999999999</v>
       </c>
-      <c r="O81" s="117">
+      <c r="O81" s="109">
         <v>4.3499999999999996</v>
       </c>
       <c r="P81" s="2">
@@ -7714,7 +7671,7 @@
       <c r="N82" s="2">
         <v>0.13900000000000001</v>
       </c>
-      <c r="O82" s="117">
+      <c r="O82" s="109">
         <v>4.17</v>
       </c>
       <c r="P82" s="2">
@@ -7782,7 +7739,7 @@
       <c r="N83" s="2">
         <v>0.09</v>
       </c>
-      <c r="O83" s="117">
+      <c r="O83" s="109">
         <v>2.6999999999999997</v>
       </c>
       <c r="P83" s="2">
@@ -7850,7 +7807,7 @@
       <c r="N84" s="2">
         <v>0.11</v>
       </c>
-      <c r="O84" s="117">
+      <c r="O84" s="109">
         <v>3.3</v>
       </c>
       <c r="P84" s="2">
@@ -7918,7 +7875,7 @@
       <c r="N85" s="2">
         <v>0.25700000000000001</v>
       </c>
-      <c r="O85" s="117">
+      <c r="O85" s="109">
         <v>7.71</v>
       </c>
       <c r="P85" s="2">
@@ -7986,7 +7943,7 @@
       <c r="N86" s="2">
         <v>0.105</v>
       </c>
-      <c r="O86" s="117">
+      <c r="O86" s="109">
         <v>3.15</v>
       </c>
       <c r="P86" s="2">
@@ -8054,7 +8011,7 @@
       <c r="N87" s="2">
         <v>0.217</v>
       </c>
-      <c r="O87" s="117">
+      <c r="O87" s="109">
         <v>6.51</v>
       </c>
       <c r="P87" s="2">
@@ -8122,7 +8079,7 @@
       <c r="N88" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O88" s="117">
+      <c r="O88" s="109">
         <v>2.1</v>
       </c>
       <c r="P88" s="2">
@@ -8190,7 +8147,7 @@
       <c r="N89" s="2">
         <v>0.14499999999999999</v>
       </c>
-      <c r="O89" s="117">
+      <c r="O89" s="109">
         <v>4.3499999999999996</v>
       </c>
       <c r="P89" s="2">
@@ -8258,7 +8215,7 @@
       <c r="N90" s="2">
         <v>1.94</v>
       </c>
-      <c r="O90" s="117">
+      <c r="O90" s="109">
         <v>58.199999999999996</v>
       </c>
       <c r="P90" s="2">
@@ -8326,7 +8283,7 @@
       <c r="N91" s="2">
         <v>0.189</v>
       </c>
-      <c r="O91" s="117">
+      <c r="O91" s="109">
         <v>5.67</v>
       </c>
       <c r="P91" s="2">
@@ -8394,7 +8351,7 @@
       <c r="N92" s="2">
         <v>0.16400000000000001</v>
       </c>
-      <c r="O92" s="117">
+      <c r="O92" s="109">
         <v>4.92</v>
       </c>
       <c r="P92" s="2">
@@ -8462,7 +8419,7 @@
       <c r="N93" s="2">
         <v>0.27100000000000002</v>
       </c>
-      <c r="O93" s="117">
+      <c r="O93" s="109">
         <v>8.1300000000000008</v>
       </c>
       <c r="P93" s="2">
@@ -8530,7 +8487,7 @@
       <c r="N94" s="2">
         <v>0.22600000000000001</v>
       </c>
-      <c r="O94" s="117">
+      <c r="O94" s="109">
         <v>6.78</v>
       </c>
       <c r="P94" s="2">
@@ -8598,7 +8555,7 @@
       <c r="N95" s="2">
         <v>0.15</v>
       </c>
-      <c r="O95" s="117">
+      <c r="O95" s="109">
         <v>4.5</v>
       </c>
       <c r="P95" s="2">
@@ -8666,7 +8623,7 @@
       <c r="N96" s="2">
         <v>0.16</v>
       </c>
-      <c r="O96" s="117">
+      <c r="O96" s="109">
         <v>4.8</v>
       </c>
       <c r="P96" s="2">
@@ -8734,7 +8691,7 @@
       <c r="N97" s="2">
         <v>0.24199999999999999</v>
       </c>
-      <c r="O97" s="117">
+      <c r="O97" s="109">
         <v>7.26</v>
       </c>
       <c r="P97" s="2">
@@ -8802,7 +8759,7 @@
       <c r="N98" s="2">
         <v>0.252</v>
       </c>
-      <c r="O98" s="117">
+      <c r="O98" s="109">
         <v>7.5600000000000005</v>
       </c>
       <c r="P98" s="2">
@@ -8870,7 +8827,7 @@
       <c r="N99" s="2">
         <v>0.216</v>
       </c>
-      <c r="O99" s="117">
+      <c r="O99" s="109">
         <v>6.4799999999999995</v>
       </c>
       <c r="P99" s="2">
@@ -8938,7 +8895,7 @@
       <c r="N100" s="2">
         <v>0.23499999999999999</v>
       </c>
-      <c r="O100" s="117">
+      <c r="O100" s="109">
         <v>7.05</v>
       </c>
       <c r="P100" s="2">
@@ -9006,7 +8963,7 @@
       <c r="N101" s="2">
         <v>0.14599999999999999</v>
       </c>
-      <c r="O101" s="117">
+      <c r="O101" s="109">
         <v>4.38</v>
       </c>
       <c r="P101" s="2">
@@ -9074,7 +9031,7 @@
       <c r="N102" s="2">
         <v>0.192</v>
       </c>
-      <c r="O102" s="117">
+      <c r="O102" s="109">
         <v>5.76</v>
       </c>
       <c r="P102" s="2">
@@ -9142,7 +9099,7 @@
       <c r="N103" s="2">
         <v>0.26100000000000001</v>
       </c>
-      <c r="O103" s="117">
+      <c r="O103" s="109">
         <v>7.83</v>
       </c>
       <c r="P103" s="2">
@@ -9210,7 +9167,7 @@
       <c r="N104" s="2">
         <v>0.36</v>
       </c>
-      <c r="O104" s="117">
+      <c r="O104" s="109">
         <v>10.799999999999999</v>
       </c>
       <c r="P104" s="2">
@@ -9278,7 +9235,7 @@
       <c r="N105" s="2">
         <v>0.187</v>
       </c>
-      <c r="O105" s="117">
+      <c r="O105" s="109">
         <v>5.61</v>
       </c>
       <c r="P105" s="2">
@@ -9346,7 +9303,7 @@
       <c r="N106" s="2">
         <v>0.29599999999999999</v>
       </c>
-      <c r="O106" s="117">
+      <c r="O106" s="109">
         <v>8.879999999999999</v>
       </c>
       <c r="P106" s="2">
@@ -9414,7 +9371,7 @@
       <c r="N107" s="2">
         <v>0.27700000000000002</v>
       </c>
-      <c r="O107" s="117">
+      <c r="O107" s="109">
         <v>8.31</v>
       </c>
       <c r="P107" s="2">
@@ -9482,7 +9439,7 @@
       <c r="N108" s="2">
         <v>0.221</v>
       </c>
-      <c r="O108" s="117">
+      <c r="O108" s="109">
         <v>6.63</v>
       </c>
       <c r="P108" s="2">
@@ -9550,7 +9507,7 @@
       <c r="N109" s="2">
         <v>0.24299999999999999</v>
       </c>
-      <c r="O109" s="117">
+      <c r="O109" s="109">
         <v>7.29</v>
       </c>
       <c r="P109" s="2">
@@ -9618,7 +9575,7 @@
       <c r="N110" s="2">
         <v>0.151</v>
       </c>
-      <c r="O110" s="117">
+      <c r="O110" s="109">
         <v>4.53</v>
       </c>
       <c r="P110" s="2">
@@ -9686,7 +9643,7 @@
       <c r="N111" s="2">
         <v>0.25800000000000001</v>
       </c>
-      <c r="O111" s="117">
+      <c r="O111" s="109">
         <v>3.87</v>
       </c>
       <c r="P111" s="2">
@@ -9754,7 +9711,7 @@
       <c r="N112" s="2">
         <v>0.629</v>
       </c>
-      <c r="O112" s="117">
+      <c r="O112" s="109">
         <v>11.100000000000001</v>
       </c>
       <c r="P112" s="2">
@@ -9822,7 +9779,7 @@
       <c r="N113" s="2">
         <v>0.50600000000000001</v>
       </c>
-      <c r="O113" s="117">
+      <c r="O113" s="109">
         <v>10.119999999999999</v>
       </c>
       <c r="P113" s="2">
@@ -9890,7 +9847,7 @@
       <c r="N114" s="2">
         <v>0.45500000000000002</v>
       </c>
-      <c r="O114" s="117">
+      <c r="O114" s="109">
         <v>7.583333333333333</v>
       </c>
       <c r="P114" s="2">
@@ -9958,7 +9915,7 @@
       <c r="N115" s="2">
         <v>0.19500000000000001</v>
       </c>
-      <c r="O115" s="117">
+      <c r="O115" s="109">
         <v>3.4411764705882355</v>
       </c>
       <c r="P115" s="2">
@@ -10026,7 +9983,7 @@
       <c r="N116" s="2">
         <v>0.76100000000000001</v>
       </c>
-      <c r="O116" s="117">
+      <c r="O116" s="109">
         <v>11.415000000000001</v>
       </c>
       <c r="P116" s="2">
@@ -10094,7 +10051,7 @@
       <c r="N117" s="2">
         <v>0.34</v>
       </c>
-      <c r="O117" s="117">
+      <c r="O117" s="109">
         <v>5.1000000000000005</v>
       </c>
       <c r="P117" s="2">
@@ -10162,7 +10119,7 @@
       <c r="N118" s="2">
         <v>0.318</v>
       </c>
-      <c r="O118" s="117">
+      <c r="O118" s="109">
         <v>4.7700000000000005</v>
       </c>
       <c r="P118" s="2">
@@ -10230,7 +10187,7 @@
       <c r="N119" s="2">
         <v>0.64300000000000002</v>
       </c>
-      <c r="O119" s="117">
+      <c r="O119" s="109">
         <v>9.6449999999999996</v>
       </c>
       <c r="P119" s="2">
@@ -10298,7 +10255,7 @@
       <c r="N120" s="2">
         <v>0.60799999999999998</v>
       </c>
-      <c r="O120" s="117">
+      <c r="O120" s="109">
         <v>9.1199999999999992</v>
       </c>
       <c r="P120" s="2">
@@ -10366,7 +10323,7 @@
       <c r="N121" s="2">
         <v>0.69399999999999995</v>
       </c>
-      <c r="O121" s="117">
+      <c r="O121" s="109">
         <v>10.957894736842105</v>
       </c>
       <c r="P121" s="2">
@@ -10434,7 +10391,7 @@
       <c r="N122" s="2">
         <v>0.76100000000000001</v>
       </c>
-      <c r="O122" s="117">
+      <c r="O122" s="109">
         <v>12.683333333333334</v>
       </c>
       <c r="P122" s="2">
@@ -10502,7 +10459,7 @@
       <c r="N123" s="2">
         <v>0.67500000000000004</v>
       </c>
-      <c r="O123" s="117">
+      <c r="O123" s="109">
         <v>10.125</v>
       </c>
       <c r="P123" s="2">
@@ -10570,7 +10527,7 @@
       <c r="N124" s="2">
         <v>0.53500000000000003</v>
       </c>
-      <c r="O124" s="117">
+      <c r="O124" s="109">
         <v>8.0250000000000004</v>
       </c>
       <c r="P124" s="2">
@@ -10638,7 +10595,7 @@
       <c r="N125" s="2">
         <v>0.309</v>
       </c>
-      <c r="O125" s="117">
+      <c r="O125" s="109">
         <v>5.4529411764705884</v>
       </c>
       <c r="P125" s="2">
@@ -10706,7 +10663,7 @@
       <c r="N126" s="2">
         <v>0.49199999999999999</v>
       </c>
-      <c r="O126" s="117">
+      <c r="O126" s="109">
         <v>7.38</v>
       </c>
       <c r="P126" s="2">
@@ -10774,7 +10731,7 @@
       <c r="N127" s="2">
         <v>1.2</v>
       </c>
-      <c r="O127" s="117">
+      <c r="O127" s="109">
         <v>25.714285714285715</v>
       </c>
       <c r="P127" s="2">
@@ -10842,7 +10799,7 @@
       <c r="N128" s="2">
         <v>0.27300000000000002</v>
       </c>
-      <c r="O128" s="117">
+      <c r="O128" s="109">
         <v>4.0950000000000006</v>
       </c>
       <c r="P128" s="2">
@@ -10910,7 +10867,7 @@
       <c r="N129" s="2">
         <v>0.7</v>
       </c>
-      <c r="O129" s="117">
+      <c r="O129" s="109">
         <v>12.352941176470589</v>
       </c>
       <c r="P129" s="2">
@@ -10978,7 +10935,7 @@
       <c r="N130" s="2">
         <v>1.58</v>
       </c>
-      <c r="O130" s="117">
+      <c r="O130" s="109">
         <v>23.700000000000003</v>
       </c>
       <c r="P130" s="2">
@@ -11046,7 +11003,7 @@
       <c r="N131" s="2">
         <v>0.58299999999999996</v>
       </c>
-      <c r="O131" s="117">
+      <c r="O131" s="109">
         <v>8.7449999999999992</v>
       </c>
       <c r="P131" s="2">
@@ -11114,7 +11071,7 @@
       <c r="N132" s="2">
         <v>0.48099999999999998</v>
       </c>
-      <c r="O132" s="117">
+      <c r="O132" s="109">
         <v>7.2149999999999999</v>
       </c>
       <c r="P132" s="2">
@@ -11182,7 +11139,7 @@
       <c r="N133" s="2">
         <v>0.46300000000000002</v>
       </c>
-      <c r="O133" s="117">
+      <c r="O133" s="109">
         <v>6.9450000000000003</v>
       </c>
       <c r="P133" s="2">
@@ -11250,7 +11207,7 @@
       <c r="N134" s="2">
         <v>0.95799999999999996</v>
       </c>
-      <c r="O134" s="117">
+      <c r="O134" s="109">
         <v>14.37</v>
       </c>
       <c r="P134" s="2">
@@ -11318,7 +11275,7 @@
       <c r="N135" s="2">
         <v>0.33400000000000002</v>
       </c>
-      <c r="O135" s="117">
+      <c r="O135" s="109">
         <v>6.6800000000000006</v>
       </c>
       <c r="P135" s="2">
@@ -11386,7 +11343,7 @@
       <c r="N136" s="2">
         <v>0.999</v>
       </c>
-      <c r="O136" s="117">
+      <c r="O136" s="109">
         <v>18.731249999999999</v>
       </c>
       <c r="P136" s="2">
@@ -11454,7 +11411,7 @@
       <c r="N137" s="2">
         <v>0.67800000000000005</v>
       </c>
-      <c r="O137" s="117">
+      <c r="O137" s="109">
         <v>10.17</v>
       </c>
       <c r="P137" s="2">
@@ -11522,7 +11479,7 @@
       <c r="N138" s="2">
         <v>0.33300000000000002</v>
       </c>
-      <c r="O138" s="117">
+      <c r="O138" s="109">
         <v>4.9950000000000001</v>
       </c>
       <c r="P138" s="2">
@@ -11590,7 +11547,7 @@
       <c r="N139" s="2">
         <v>0.51400000000000001</v>
       </c>
-      <c r="O139" s="117">
+      <c r="O139" s="109">
         <v>11.014285714285714</v>
       </c>
       <c r="P139" s="2">
@@ -11658,7 +11615,7 @@
       <c r="N140" s="2">
         <v>0.59</v>
       </c>
-      <c r="O140" s="117">
+      <c r="O140" s="109">
         <v>8.85</v>
       </c>
       <c r="P140" s="2">
@@ -11726,7 +11683,7 @@
       <c r="N141" s="2">
         <v>0.93400000000000005</v>
       </c>
-      <c r="O141" s="117">
+      <c r="O141" s="109">
         <v>18.680000000000003</v>
       </c>
       <c r="P141" s="2">
@@ -11794,7 +11751,7 @@
       <c r="N142" s="2">
         <v>0.35599999999999998</v>
       </c>
-      <c r="O142" s="117">
+      <c r="O142" s="109">
         <v>5.34</v>
       </c>
       <c r="P142" s="2">
@@ -11862,7 +11819,7 @@
       <c r="N143" s="2">
         <v>0.73799999999999999</v>
       </c>
-      <c r="O143" s="117">
+      <c r="O143" s="109">
         <v>14.76</v>
       </c>
       <c r="P143" s="2">
@@ -11930,7 +11887,7 @@
       <c r="N144" s="2">
         <v>0.84899999999999998</v>
       </c>
-      <c r="O144" s="117">
+      <c r="O144" s="109">
         <v>12.734999999999999</v>
       </c>
       <c r="P144" s="2">
@@ -11998,7 +11955,7 @@
       <c r="N145" s="2">
         <v>0.39700000000000002</v>
       </c>
-      <c r="O145" s="117">
+      <c r="O145" s="109">
         <v>5.9550000000000001</v>
       </c>
       <c r="P145" s="2">
@@ -12066,7 +12023,7 @@
       <c r="N146" s="2">
         <v>0.70799999999999996</v>
       </c>
-      <c r="O146" s="117">
+      <c r="O146" s="109">
         <v>14.159999999999998</v>
       </c>
       <c r="P146" s="2">
@@ -12134,7 +12091,7 @@
       <c r="N147" s="2">
         <v>0.34799999999999998</v>
       </c>
-      <c r="O147" s="117">
+      <c r="O147" s="109">
         <v>5.22</v>
       </c>
       <c r="P147" s="2">
@@ -12202,7 +12159,7 @@
       <c r="N148" s="2">
         <v>0.47499999999999998</v>
       </c>
-      <c r="O148" s="117">
+      <c r="O148" s="109">
         <v>9.5</v>
       </c>
       <c r="P148" s="2">
@@ -12270,7 +12227,7 @@
       <c r="N149" s="2">
         <v>0.433</v>
       </c>
-      <c r="O149" s="117">
+      <c r="O149" s="109">
         <v>6.4950000000000001</v>
       </c>
       <c r="P149" s="2">
@@ -12338,7 +12295,7 @@
       <c r="N150" s="2">
         <v>0.35099999999999998</v>
       </c>
-      <c r="O150" s="117">
+      <c r="O150" s="109">
         <v>6.1941176470588237</v>
       </c>
       <c r="P150" s="2">
@@ -12406,7 +12363,7 @@
       <c r="N151" s="2">
         <v>0.83699999999999997</v>
       </c>
-      <c r="O151" s="117">
+      <c r="O151" s="109">
         <v>12.555</v>
       </c>
       <c r="P151" s="2">
@@ -12474,7 +12431,7 @@
       <c r="N152" s="2">
         <v>1.34</v>
       </c>
-      <c r="O152" s="117">
+      <c r="O152" s="109">
         <v>22.333333333333336</v>
       </c>
       <c r="P152" s="2">
@@ -12542,7 +12499,7 @@
       <c r="N153" s="2">
         <v>0.42799999999999999</v>
       </c>
-      <c r="O153" s="117">
+      <c r="O153" s="109">
         <v>7.1333333333333329</v>
       </c>
       <c r="P153" s="2">
@@ -12610,7 +12567,7 @@
       <c r="N154" s="2">
         <v>1.48</v>
       </c>
-      <c r="O154" s="117">
+      <c r="O154" s="109">
         <v>22.2</v>
       </c>
       <c r="P154" s="2">
@@ -12678,7 +12635,7 @@
       <c r="N155" s="2">
         <v>0.40100000000000002</v>
       </c>
-      <c r="O155" s="117">
+      <c r="O155" s="109">
         <v>6.0150000000000006</v>
       </c>
       <c r="P155" s="2">
@@ -12746,7 +12703,7 @@
       <c r="N156" s="2">
         <v>0.35299999999999998</v>
       </c>
-      <c r="O156" s="117">
+      <c r="O156" s="109">
         <v>7.06</v>
       </c>
       <c r="P156" s="2">
@@ -12814,7 +12771,7 @@
       <c r="N157" s="2">
         <v>0.67500000000000004</v>
       </c>
-      <c r="O157" s="117">
+      <c r="O157" s="109">
         <v>13.5</v>
       </c>
       <c r="P157" s="2">
@@ -12882,7 +12839,7 @@
       <c r="N158" s="2">
         <v>0.47099999999999997</v>
       </c>
-      <c r="O158" s="117">
+      <c r="O158" s="109">
         <v>7.4368421052631577</v>
       </c>
       <c r="P158" s="2">
@@ -12950,7 +12907,7 @@
       <c r="N159" s="2">
         <v>0.88119999999999998</v>
       </c>
-      <c r="O159" s="117">
+      <c r="O159" s="109">
         <v>13.218</v>
       </c>
       <c r="P159" s="2">
@@ -13018,7 +12975,7 @@
       <c r="N160" s="2">
         <v>1.1100000000000001</v>
       </c>
-      <c r="O160" s="117">
+      <c r="O160" s="109">
         <v>16.650000000000002</v>
       </c>
       <c r="P160" s="2">
@@ -13086,7 +13043,7 @@
       <c r="N161" s="2">
         <v>0.47299999999999998</v>
       </c>
-      <c r="O161" s="117">
+      <c r="O161" s="109">
         <v>7.8833333333333329</v>
       </c>
       <c r="P161" s="2">
@@ -13154,7 +13111,7 @@
       <c r="N162" s="2">
         <v>1.49</v>
       </c>
-      <c r="O162" s="117">
+      <c r="O162" s="109">
         <v>24.833333333333336</v>
       </c>
       <c r="P162" s="2">
@@ -13222,7 +13179,7 @@
       <c r="N163" s="2">
         <v>0.95399999999999996</v>
       </c>
-      <c r="O163" s="117">
+      <c r="O163" s="109">
         <v>16.835294117647059</v>
       </c>
       <c r="P163" s="2">
@@ -13290,7 +13247,7 @@
       <c r="N164" s="2">
         <v>0.36699999999999999</v>
       </c>
-      <c r="O164" s="117">
+      <c r="O164" s="109">
         <v>6.4764705882352942</v>
       </c>
       <c r="P164" s="2">
@@ -13358,7 +13315,7 @@
       <c r="N165" s="2">
         <v>0.94799999999999995</v>
       </c>
-      <c r="O165" s="117">
+      <c r="O165" s="109">
         <v>14.968421052631578</v>
       </c>
       <c r="P165" s="2">
@@ -13426,7 +13383,7 @@
       <c r="N166" s="2">
         <v>0.73899999999999999</v>
       </c>
-      <c r="O166" s="117">
+      <c r="O166" s="109">
         <v>11.084999999999999</v>
       </c>
       <c r="P166" s="2">
@@ -13494,7 +13451,7 @@
       <c r="N167" s="2">
         <v>1.01</v>
       </c>
-      <c r="O167" s="117">
+      <c r="O167" s="109">
         <v>15.15</v>
       </c>
       <c r="P167" s="2">
@@ -13562,7 +13519,7 @@
       <c r="N168" s="2">
         <v>1.27</v>
       </c>
-      <c r="O168" s="117">
+      <c r="O168" s="109">
         <v>20.05263157894737</v>
       </c>
       <c r="P168" s="2">
@@ -13630,7 +13587,7 @@
       <c r="N169" s="2">
         <v>0.67500000000000004</v>
       </c>
-      <c r="O169" s="117">
+      <c r="O169" s="109">
         <v>10.125</v>
       </c>
       <c r="P169" s="2">
@@ -13698,7 +13655,7 @@
       <c r="N170" s="2">
         <v>0.55100000000000005</v>
       </c>
-      <c r="O170" s="117">
+      <c r="O170" s="109">
         <v>11.020000000000001</v>
       </c>
       <c r="P170" s="2">
@@ -13766,7 +13723,7 @@
       <c r="N171" s="2">
         <v>6.4</v>
       </c>
-      <c r="O171" s="117">
+      <c r="O171" s="109">
         <v>101.05263157894737</v>
       </c>
       <c r="P171" s="2">
@@ -13834,7 +13791,7 @@
       <c r="N172" s="2">
         <v>5.2</v>
       </c>
-      <c r="O172" s="117">
+      <c r="O172" s="109">
         <v>78</v>
       </c>
       <c r="P172" s="2">
@@ -13902,7 +13859,7 @@
       <c r="N173" s="2">
         <v>0.27600000000000002</v>
       </c>
-      <c r="O173" s="117">
+      <c r="O173" s="109">
         <v>4.6000000000000005</v>
       </c>
       <c r="P173" s="2">
@@ -13970,7 +13927,7 @@
       <c r="N174" s="2">
         <v>0.59599999999999997</v>
       </c>
-      <c r="O174" s="117">
+      <c r="O174" s="109">
         <v>8.94</v>
       </c>
       <c r="P174" s="2">
@@ -14038,7 +13995,7 @@
       <c r="N175" s="2">
         <v>0.24199999999999999</v>
       </c>
-      <c r="O175" s="117">
+      <c r="O175" s="109">
         <v>4.0333333333333332</v>
       </c>
       <c r="P175" s="2">
@@ -14106,7 +14063,7 @@
       <c r="N176" s="2">
         <v>0.57299999999999995</v>
       </c>
-      <c r="O176" s="117">
+      <c r="O176" s="109">
         <v>10.111764705882353</v>
       </c>
       <c r="P176" s="2">
@@ -14174,7 +14131,7 @@
       <c r="N177" s="2">
         <v>0.753</v>
       </c>
-      <c r="O177" s="117">
+      <c r="O177" s="109">
         <v>12.549999999999999</v>
       </c>
       <c r="P177" s="2">
@@ -14200,12 +14157,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V177" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A67:A177 A1:A51">
+    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B178:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A67:A177 A1:A51">
-    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14312,7 +14270,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="116" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -14399,7 +14357,7 @@
       </c>
       <c r="J2" s="40"/>
       <c r="K2" s="63">
-        <f>D2*25</f>
+        <f t="shared" ref="K2:K33" si="0">D2*25</f>
         <v>8.125</v>
       </c>
       <c r="L2">
@@ -14422,7 +14380,7 @@
       <c r="B3" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="32">
@@ -14443,15 +14401,15 @@
       </c>
       <c r="J3" s="40"/>
       <c r="K3" s="63">
-        <f>D3*25</f>
+        <f t="shared" si="0"/>
         <v>6.45</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L65" si="0">IF(5/D3&gt;18,18,5/D3)</f>
+        <f t="shared" ref="L3:L65" si="1">IF(5/D3&gt;18,18,5/D3)</f>
         <v>18</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M64" si="1">(25-L3)*D3</f>
+        <f t="shared" ref="M3:M64" si="2">(25-L3)*D3</f>
         <v>1.806</v>
       </c>
       <c r="N3" s="63" t="s">
@@ -14466,7 +14424,7 @@
       <c r="B4" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="11" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="32">
@@ -14487,15 +14445,15 @@
       </c>
       <c r="J4" s="40"/>
       <c r="K4" s="63">
-        <f>D4*25</f>
+        <f t="shared" si="0"/>
         <v>3.8249999999999997</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.071</v>
       </c>
       <c r="N4" s="63" t="s">
@@ -14533,15 +14491,15 @@
       </c>
       <c r="J5" s="57"/>
       <c r="K5" s="63">
-        <f>D5*25</f>
+        <f t="shared" si="0"/>
         <v>12.45</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.040160642570282</v>
       </c>
       <c r="M5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.4499999999999993</v>
       </c>
       <c r="N5" s="63" t="s">
@@ -14581,15 +14539,15 @@
         <v>286</v>
       </c>
       <c r="K6" s="63">
-        <f>D6*25</f>
+        <f t="shared" si="0"/>
         <v>22.05</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.6689342403628116</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17.05</v>
       </c>
       <c r="N6" s="63" t="s">
@@ -14629,15 +14587,15 @@
         <v>286</v>
       </c>
       <c r="K7" s="63">
-        <f>D7*25</f>
+        <f t="shared" si="0"/>
         <v>16.125</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.7519379844961236</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.125</v>
       </c>
       <c r="N7" s="63" t="s">
@@ -14677,15 +14635,15 @@
         <v>286</v>
       </c>
       <c r="K8" s="63">
-        <f>D8*25</f>
+        <f t="shared" si="0"/>
         <v>12.25</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.204081632653061</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.25</v>
       </c>
       <c r="N8" s="63" t="s">
@@ -14725,15 +14683,15 @@
         <v>286</v>
       </c>
       <c r="K9" s="63">
-        <f>D9*25</f>
+        <f t="shared" si="0"/>
         <v>11.725</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.660980810234543</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.7249999999999988</v>
       </c>
       <c r="N9" s="63" t="s">
@@ -14748,7 +14706,7 @@
       <c r="B10" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="11" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="12">
@@ -14773,15 +14731,15 @@
         <v>286</v>
       </c>
       <c r="K10" s="63">
-        <f>D10*25</f>
+        <f t="shared" si="0"/>
         <v>6.5750000000000002</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8410000000000002</v>
       </c>
       <c r="N10" s="63" t="s">
@@ -14821,15 +14779,15 @@
         <v>286</v>
       </c>
       <c r="K11" s="63">
-        <f>D11*25</f>
+        <f t="shared" si="0"/>
         <v>12.275</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.183299389002038</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.2749999999999995</v>
       </c>
       <c r="N11" s="63" t="s">
@@ -14869,15 +14827,15 @@
         <v>286</v>
       </c>
       <c r="K12" s="63">
-        <f>D12*25</f>
+        <f t="shared" si="0"/>
         <v>9.75</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.820512820512819</v>
       </c>
       <c r="M12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.7500000000000009</v>
       </c>
       <c r="N12" s="63" t="s">
@@ -14917,15 +14875,15 @@
         <v>286</v>
       </c>
       <c r="K13" s="63">
-        <f>D13*25</f>
+        <f t="shared" si="0"/>
         <v>9.1</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13.736263736263737</v>
       </c>
       <c r="M13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="N13" s="63" t="s">
@@ -14965,15 +14923,15 @@
         <v>286</v>
       </c>
       <c r="K14" s="63">
-        <f>D14*25</f>
+        <f t="shared" si="0"/>
         <v>10.050000000000001</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.437810945273631</v>
       </c>
       <c r="M14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.0500000000000007</v>
       </c>
       <c r="N14" s="63" t="s">
@@ -15013,15 +14971,15 @@
         <v>286</v>
       </c>
       <c r="K15" s="63">
-        <f>D15*25</f>
+        <f t="shared" si="0"/>
         <v>14.299999999999999</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7412587412587417</v>
       </c>
       <c r="M15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="N15" s="63" t="s">
@@ -15061,15 +15019,15 @@
         <v>286</v>
       </c>
       <c r="K16" s="63">
-        <f>D16*25</f>
+        <f t="shared" si="0"/>
         <v>19.950000000000003</v>
       </c>
       <c r="L16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.2656641604010019</v>
       </c>
       <c r="M16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.950000000000001</v>
       </c>
       <c r="N16" s="63" t="s">
@@ -15105,15 +15063,15 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="K17" s="63">
-        <f>D17*25</f>
+        <f t="shared" si="0"/>
         <v>9.7000000000000011</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.88659793814433</v>
       </c>
       <c r="M17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.7</v>
       </c>
       <c r="N17" s="63" t="s">
@@ -15149,15 +15107,15 @@
         <v>21.875</v>
       </c>
       <c r="K18" s="63">
-        <f>D18*25</f>
+        <f t="shared" si="0"/>
         <v>21.875</v>
       </c>
       <c r="L18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7142857142857144</v>
       </c>
       <c r="M18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.875</v>
       </c>
       <c r="N18" s="63" t="s">
@@ -15195,15 +15153,15 @@
       </c>
       <c r="J19" s="33"/>
       <c r="K19" s="63">
-        <f>D19*25</f>
+        <f t="shared" si="0"/>
         <v>31.25</v>
       </c>
       <c r="L19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="M19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.25</v>
       </c>
       <c r="N19" s="63" t="s">
@@ -15241,15 +15199,15 @@
       </c>
       <c r="J20" s="33"/>
       <c r="K20" s="63">
-        <f>D20*25</f>
+        <f t="shared" si="0"/>
         <v>7.7750000000000004</v>
       </c>
       <c r="L20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.077170418006432</v>
       </c>
       <c r="M20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.7749999999999995</v>
       </c>
       <c r="N20" s="63" t="s">
@@ -15287,15 +15245,15 @@
       </c>
       <c r="J21" s="33"/>
       <c r="K21" s="63">
-        <f>D21*25</f>
+        <f t="shared" si="0"/>
         <v>10.199999999999999</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.254901960784315</v>
       </c>
       <c r="M21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1999999999999993</v>
       </c>
       <c r="N21" s="63" t="s">
@@ -15333,15 +15291,15 @@
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="63">
-        <f>D22*25</f>
+        <f t="shared" si="0"/>
         <v>11.55</v>
       </c>
       <c r="L22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.822510822510822</v>
       </c>
       <c r="M22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.5500000000000007</v>
       </c>
       <c r="N22" s="63" t="s">
@@ -15379,15 +15337,15 @@
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="63">
-        <f>D23*25</f>
+        <f t="shared" si="0"/>
         <v>10.574999999999999</v>
       </c>
       <c r="L23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.82033096926714</v>
       </c>
       <c r="M23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.5750000000000002</v>
       </c>
       <c r="N23" s="63" t="s">
@@ -15425,15 +15383,15 @@
       </c>
       <c r="J24" s="55"/>
       <c r="K24" s="63">
-        <f>D24*25</f>
+        <f t="shared" si="0"/>
         <v>18.350000000000001</v>
       </c>
       <c r="L24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.8119891008174385</v>
       </c>
       <c r="M24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.35</v>
       </c>
       <c r="N24" s="63" t="s">
@@ -15469,15 +15427,15 @@
       </c>
       <c r="J25" s="40"/>
       <c r="K25" s="63">
-        <f>D25*25</f>
+        <f t="shared" si="0"/>
         <v>7.35</v>
       </c>
       <c r="L25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17.006802721088437</v>
       </c>
       <c r="M25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3499999999999992</v>
       </c>
       <c r="N25" s="63" t="s">
@@ -15513,15 +15471,15 @@
       </c>
       <c r="J26" s="40"/>
       <c r="K26" s="63">
-        <f>D26*25</f>
+        <f t="shared" si="0"/>
         <v>8.2750000000000004</v>
       </c>
       <c r="L26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.105740181268882</v>
       </c>
       <c r="M26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.2750000000000004</v>
       </c>
       <c r="N26" s="63" t="s">
@@ -15557,15 +15515,15 @@
       </c>
       <c r="J27" s="40"/>
       <c r="K27" s="63">
-        <f>D27*25</f>
+        <f t="shared" si="0"/>
         <v>12.8</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.765625</v>
       </c>
       <c r="M27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.8</v>
       </c>
       <c r="N27" s="63" t="s">
@@ -15601,15 +15559,15 @@
       </c>
       <c r="J28" s="54"/>
       <c r="K28" s="63">
-        <f>D28*25</f>
+        <f t="shared" si="0"/>
         <v>11.824999999999999</v>
       </c>
       <c r="L28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.570824524312897</v>
       </c>
       <c r="M28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.8249999999999993</v>
       </c>
       <c r="N28" s="63" t="s">
@@ -15645,15 +15603,15 @@
       </c>
       <c r="J29" s="54"/>
       <c r="K29" s="63">
-        <f>D29*25</f>
+        <f t="shared" si="0"/>
         <v>8.0750000000000011</v>
       </c>
       <c r="L29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.479876160990711</v>
       </c>
       <c r="M29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0750000000000002</v>
       </c>
       <c r="N29" s="63" t="s">
@@ -15689,15 +15647,15 @@
       </c>
       <c r="J30" s="40"/>
       <c r="K30" s="63">
-        <f>D30*25</f>
+        <f t="shared" si="0"/>
         <v>27.750000000000004</v>
       </c>
       <c r="L30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.5045045045045038</v>
       </c>
       <c r="M30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22.750000000000004</v>
       </c>
       <c r="N30" s="63" t="s">
@@ -15735,15 +15693,15 @@
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="63">
-        <f>D31*25</f>
+        <f t="shared" si="0"/>
         <v>10.100000000000001</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.376237623762375</v>
       </c>
       <c r="M31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1000000000000005</v>
       </c>
       <c r="N31" s="63" t="s">
@@ -15781,15 +15739,15 @@
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="63">
-        <f>D32*25</f>
+        <f t="shared" si="0"/>
         <v>14.299999999999999</v>
       </c>
       <c r="L32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7412587412587417</v>
       </c>
       <c r="M32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="N32" s="63" t="s">
@@ -15804,7 +15762,7 @@
       <c r="B33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="C33" s="106" t="s">
+      <c r="C33" s="11" t="s">
         <v>189</v>
       </c>
       <c r="D33" s="12">
@@ -15827,15 +15785,15 @@
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="63">
-        <f>D33*25</f>
+        <f t="shared" si="0"/>
         <v>6.1749999999999998</v>
       </c>
       <c r="L33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7290000000000001</v>
       </c>
       <c r="N33" s="63" t="s">
@@ -15873,15 +15831,15 @@
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="63">
-        <f>D34*25</f>
+        <f t="shared" ref="K34:K65" si="3">D34*25</f>
         <v>14.224999999999998</v>
       </c>
       <c r="L34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7873462214411262</v>
       </c>
       <c r="M34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.2249999999999979</v>
       </c>
       <c r="N34" s="63" t="s">
@@ -15919,15 +15877,15 @@
       </c>
       <c r="J35" s="40"/>
       <c r="K35" s="63">
-        <f>D35*25</f>
+        <f t="shared" si="3"/>
         <v>11.125</v>
       </c>
       <c r="L35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.235955056179774</v>
       </c>
       <c r="M35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.1250000000000009</v>
       </c>
       <c r="N35" s="63" t="s">
@@ -15942,7 +15900,7 @@
       <c r="B36" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="C36" s="106" t="s">
+      <c r="C36" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D36" s="12">
@@ -15965,15 +15923,15 @@
       </c>
       <c r="J36" s="40"/>
       <c r="K36" s="63">
-        <f>D36*25</f>
+        <f t="shared" si="3"/>
         <v>5.2749999999999995</v>
       </c>
       <c r="L36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4769999999999999</v>
       </c>
       <c r="N36" s="63" t="s">
@@ -16011,15 +15969,15 @@
       </c>
       <c r="J37" s="40"/>
       <c r="K37" s="63">
-        <f>D37*25</f>
+        <f t="shared" si="3"/>
         <v>14.149999999999999</v>
       </c>
       <c r="L37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.8339222614840995</v>
       </c>
       <c r="M37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.15</v>
       </c>
       <c r="N37" s="63" t="s">
@@ -16034,7 +15992,7 @@
       <c r="B38" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="C38" s="106" t="s">
+      <c r="C38" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D38" s="12">
@@ -16057,15 +16015,15 @@
       </c>
       <c r="J38" s="40"/>
       <c r="K38" s="63">
-        <f>D38*25</f>
+        <f t="shared" si="3"/>
         <v>6.2249999999999996</v>
       </c>
       <c r="L38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7429999999999999</v>
       </c>
       <c r="N38" s="63" t="s">
@@ -16103,15 +16061,15 @@
       </c>
       <c r="J39" s="58"/>
       <c r="K39" s="63">
-        <f>D39*25</f>
+        <f t="shared" si="3"/>
         <v>7.55</v>
       </c>
       <c r="L39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.556291390728479</v>
       </c>
       <c r="M39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5499999999999994</v>
       </c>
       <c r="N39" s="63" t="s">
@@ -16149,15 +16107,15 @@
       </c>
       <c r="J40" s="58"/>
       <c r="K40" s="63">
-        <f>D40*25</f>
+        <f t="shared" si="3"/>
         <v>8.0500000000000007</v>
       </c>
       <c r="L40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.527950310559007</v>
       </c>
       <c r="M40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.05</v>
       </c>
       <c r="N40" s="63" t="s">
@@ -16172,7 +16130,7 @@
       <c r="B41" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="C41" s="106" t="s">
+      <c r="C41" s="11" t="s">
         <v>56</v>
       </c>
       <c r="D41" s="12">
@@ -16195,15 +16153,15 @@
       </c>
       <c r="J41" s="58"/>
       <c r="K41" s="63">
-        <f>D41*25</f>
+        <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
       <c r="L41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.47</v>
       </c>
       <c r="N41" s="63" t="s">
@@ -16241,15 +16199,15 @@
       </c>
       <c r="J42" s="58"/>
       <c r="K42" s="63">
-        <f>D42*25</f>
+        <f t="shared" si="3"/>
         <v>8.35</v>
       </c>
       <c r="L42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14.97005988023952</v>
       </c>
       <c r="M42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.3500000000000005</v>
       </c>
       <c r="N42" s="63" t="s">
@@ -16289,15 +16247,15 @@
       </c>
       <c r="J43" s="58"/>
       <c r="K43" s="63">
-        <f>D43*25</f>
+        <f t="shared" si="3"/>
         <v>15.174999999999999</v>
       </c>
       <c r="L43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.2372322899505761</v>
       </c>
       <c r="M43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.175000000000001</v>
       </c>
       <c r="N43" s="63" t="s">
@@ -16335,15 +16293,15 @@
       </c>
       <c r="J44" s="58"/>
       <c r="K44" s="63">
-        <f>D44*25</f>
+        <f t="shared" si="3"/>
         <v>10.574999999999999</v>
       </c>
       <c r="L44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.82033096926714</v>
       </c>
       <c r="M44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.5750000000000002</v>
       </c>
       <c r="N44" s="63" t="s">
@@ -16381,15 +16339,15 @@
       </c>
       <c r="J45" s="58"/>
       <c r="K45" s="63">
-        <f>D45*25</f>
+        <f t="shared" si="3"/>
         <v>8.2249999999999996</v>
       </c>
       <c r="L45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.19756838905775</v>
       </c>
       <c r="M45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.2250000000000005</v>
       </c>
       <c r="N45" s="63" t="s">
@@ -16427,15 +16385,15 @@
       </c>
       <c r="J46" s="58"/>
       <c r="K46" s="63">
-        <f>D46*25</f>
+        <f t="shared" si="3"/>
         <v>10.125</v>
       </c>
       <c r="L46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.345679012345679</v>
       </c>
       <c r="M46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.125</v>
       </c>
       <c r="N46" s="63" t="s">
@@ -16473,15 +16431,15 @@
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="63">
-        <f>D47*25</f>
+        <f t="shared" si="3"/>
         <v>14.374999999999998</v>
       </c>
       <c r="L47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.6956521739130448</v>
       </c>
       <c r="M47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.3749999999999982</v>
       </c>
       <c r="N47" s="63" t="s">
@@ -16519,15 +16477,15 @@
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="63">
-        <f>D48*25</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="L48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.416666666666668</v>
       </c>
       <c r="M48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.9999999999999991</v>
       </c>
       <c r="N48" s="63" t="s">
@@ -16565,15 +16523,15 @@
       </c>
       <c r="J49" s="13"/>
       <c r="K49" s="63">
-        <f>D49*25</f>
+        <f t="shared" si="3"/>
         <v>18.675000000000001</v>
       </c>
       <c r="L49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.6934404283801872</v>
       </c>
       <c r="M49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.675000000000001</v>
       </c>
       <c r="N49" s="63" t="s">
@@ -16611,15 +16569,15 @@
       </c>
       <c r="J50" s="13"/>
       <c r="K50" s="63">
-        <f>D50*25</f>
+        <f t="shared" si="3"/>
         <v>9.4749999999999996</v>
       </c>
       <c r="L50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13.192612137203167</v>
       </c>
       <c r="M50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4749999999999996</v>
       </c>
       <c r="N50" s="63" t="s">
@@ -16634,7 +16592,7 @@
       <c r="B51" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C51" s="106" t="s">
+      <c r="C51" s="11" t="s">
         <v>67</v>
       </c>
       <c r="D51" s="12">
@@ -16657,15 +16615,15 @@
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="63">
-        <f>D51*25</f>
+        <f t="shared" si="3"/>
         <v>5.0750000000000002</v>
       </c>
       <c r="L51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.421</v>
       </c>
       <c r="N51" s="63" t="s">
@@ -16680,7 +16638,7 @@
       <c r="B52" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="C52" s="107" t="s">
+      <c r="C52" s="26" t="s">
         <v>69</v>
       </c>
       <c r="D52" s="12">
@@ -16703,15 +16661,15 @@
         <v>6.85</v>
       </c>
       <c r="K52" s="63">
-        <f>D52*25</f>
+        <f t="shared" si="3"/>
         <v>6.8500000000000005</v>
       </c>
       <c r="L52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.9180000000000001</v>
       </c>
       <c r="N52" s="63" t="s">
@@ -16749,15 +16707,15 @@
         <v>9.8249999999999993</v>
       </c>
       <c r="K53" s="63">
-        <f>D53*25</f>
+        <f t="shared" si="3"/>
         <v>9.8250000000000011</v>
       </c>
       <c r="L53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.72264631043257</v>
       </c>
       <c r="M53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8250000000000002</v>
       </c>
       <c r="N53" s="63" t="s">
@@ -16795,15 +16753,15 @@
         <v>7.45</v>
       </c>
       <c r="K54" s="63">
-        <f>D54*25</f>
+        <f t="shared" si="3"/>
         <v>7.4499999999999993</v>
       </c>
       <c r="L54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.778523489932887</v>
       </c>
       <c r="M54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4499999999999997</v>
       </c>
       <c r="N54" s="63" t="s">
@@ -16841,15 +16799,15 @@
         <v>19.399999999999999</v>
       </c>
       <c r="K55" s="63">
-        <f>D55*25</f>
+        <f t="shared" si="3"/>
         <v>19.400000000000002</v>
       </c>
       <c r="L55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.4432989690721651</v>
       </c>
       <c r="M55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.399999999999999</v>
       </c>
       <c r="N55" s="63" t="s">
@@ -16887,15 +16845,15 @@
         <v>19.45</v>
       </c>
       <c r="K56" s="63">
-        <f>D56*25</f>
+        <f t="shared" si="3"/>
         <v>19.45</v>
       </c>
       <c r="L56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.4267352185089974</v>
       </c>
       <c r="M56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.45</v>
       </c>
       <c r="N56" s="63" t="s">
@@ -16931,15 +16889,15 @@
       </c>
       <c r="J57" s="13"/>
       <c r="K57" s="63">
-        <f>D57*25</f>
+        <f t="shared" si="3"/>
         <v>18.224999999999998</v>
       </c>
       <c r="L57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.8587105624142666</v>
       </c>
       <c r="M57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.225</v>
       </c>
       <c r="N57" s="63" t="s">
@@ -16954,7 +16912,7 @@
       <c r="B58" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="C58" s="108" t="s">
+      <c r="C58" s="13" t="s">
         <v>75</v>
       </c>
       <c r="D58" s="12">
@@ -16975,15 +16933,15 @@
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="63">
-        <f>D58*25</f>
+        <f t="shared" si="3"/>
         <v>6.25</v>
       </c>
       <c r="L58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
       <c r="N58" s="63" t="s">
@@ -17019,15 +16977,15 @@
       </c>
       <c r="J59" s="40"/>
       <c r="K59" s="63">
-        <f>D59*25</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="L59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.032258064516129</v>
       </c>
       <c r="M59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="N59" s="63" t="s">
@@ -17063,15 +17021,15 @@
       </c>
       <c r="J60" s="40"/>
       <c r="K60" s="63">
-        <f>D60*25</f>
+        <f t="shared" si="3"/>
         <v>14.424999999999999</v>
       </c>
       <c r="L60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.6655112651646462</v>
       </c>
       <c r="M60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.4249999999999989</v>
       </c>
       <c r="N60" s="63" t="s">
@@ -17086,7 +17044,7 @@
       <c r="B61" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="C61" s="109" t="s">
+      <c r="C61" s="45" t="s">
         <v>79</v>
       </c>
       <c r="D61" s="34">
@@ -17109,15 +17067,15 @@
       </c>
       <c r="J61" s="13"/>
       <c r="K61" s="63">
-        <f>D61*25</f>
+        <f t="shared" si="3"/>
         <v>6.1</v>
       </c>
       <c r="L61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="M61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.708</v>
       </c>
       <c r="N61" s="63" t="s">
@@ -17155,15 +17113,15 @@
       </c>
       <c r="J62" s="13"/>
       <c r="K62" s="63">
-        <f>D62*25</f>
+        <f t="shared" si="3"/>
         <v>33.5</v>
       </c>
       <c r="L62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.7313432835820892</v>
       </c>
       <c r="M62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28.500000000000004</v>
       </c>
       <c r="N62" s="63" t="s">
@@ -17201,15 +17159,15 @@
       </c>
       <c r="J63" s="40"/>
       <c r="K63" s="63">
-        <f>D63*25</f>
+        <f t="shared" si="3"/>
         <v>16.75</v>
       </c>
       <c r="L63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.4626865671641784</v>
       </c>
       <c r="M63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.750000000000002</v>
       </c>
       <c r="N63" s="63" t="s">
@@ -17247,15 +17205,15 @@
       </c>
       <c r="J64" s="40"/>
       <c r="K64" s="63">
-        <f>D64*25</f>
+        <f t="shared" si="3"/>
         <v>12.375</v>
       </c>
       <c r="L64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.1010101010101</v>
       </c>
       <c r="M64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.375</v>
       </c>
       <c r="N64" s="63" t="s">
@@ -17293,15 +17251,15 @@
       </c>
       <c r="J65" s="40"/>
       <c r="K65" s="63">
-        <f>D65*25</f>
+        <f t="shared" si="3"/>
         <v>11.15</v>
       </c>
       <c r="L65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.210762331838565</v>
       </c>
       <c r="M65">
-        <f t="shared" ref="M65:M128" si="2">(25-L65)*D65</f>
+        <f t="shared" ref="M65:M128" si="4">(25-L65)*D65</f>
         <v>6.15</v>
       </c>
       <c r="N65" s="63" t="s">
@@ -17339,15 +17297,15 @@
       </c>
       <c r="J66" s="40"/>
       <c r="K66" s="63">
-        <f>D66*25</f>
+        <f t="shared" ref="K66:K97" si="5">D66*25</f>
         <v>9</v>
       </c>
       <c r="L66">
-        <f t="shared" ref="L66:L129" si="3">IF(5/D66&gt;18,18,5/D66)</f>
+        <f t="shared" ref="L66:L129" si="6">IF(5/D66&gt;18,18,5/D66)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="M66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.9999999999999996</v>
       </c>
       <c r="N66" s="63" t="s">
@@ -17383,15 +17341,15 @@
       </c>
       <c r="J67" s="13"/>
       <c r="K67" s="63">
-        <f>D67*25</f>
+        <f t="shared" si="5"/>
         <v>8.125</v>
       </c>
       <c r="L67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15.384615384615383</v>
       </c>
       <c r="M67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.1250000000000004</v>
       </c>
       <c r="N67" s="63" t="s">
@@ -17427,15 +17385,15 @@
       </c>
       <c r="J68" s="13"/>
       <c r="K68" s="63">
-        <f>D68*25</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="L68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="M68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="N68" s="63" t="s">
@@ -17471,15 +17429,15 @@
       </c>
       <c r="J69" s="13"/>
       <c r="K69" s="63">
-        <f>D69*25</f>
+        <f t="shared" si="5"/>
         <v>8.25</v>
       </c>
       <c r="L69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15.15151515151515</v>
       </c>
       <c r="M69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.2500000000000004</v>
       </c>
       <c r="N69" s="63" t="s">
@@ -17515,15 +17473,15 @@
       </c>
       <c r="J70" s="13"/>
       <c r="K70" s="63">
-        <f>D70*25</f>
+        <f t="shared" si="5"/>
         <v>13.900000000000002</v>
       </c>
       <c r="L70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.9928057553956826</v>
       </c>
       <c r="M70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.9000000000000021</v>
       </c>
       <c r="N70" s="63" t="s">
@@ -17561,15 +17519,15 @@
       </c>
       <c r="J71" s="13"/>
       <c r="K71" s="63">
-        <f>D71*25</f>
+        <f t="shared" si="5"/>
         <v>7.1499999999999995</v>
       </c>
       <c r="L71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17.482517482517483</v>
       </c>
       <c r="M71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1499999999999995</v>
       </c>
       <c r="N71" s="63" t="s">
@@ -17603,15 +17561,15 @@
       </c>
       <c r="J72" s="40"/>
       <c r="K72" s="63">
-        <f>D72*25</f>
+        <f t="shared" si="5"/>
         <v>76.25</v>
       </c>
       <c r="L72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.639344262295082</v>
       </c>
       <c r="M72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>71.25</v>
       </c>
       <c r="N72" s="63" t="s">
@@ -17645,15 +17603,15 @@
       </c>
       <c r="J73" s="40"/>
       <c r="K73" s="63">
-        <f>D73*25</f>
+        <f t="shared" si="5"/>
         <v>21.824999999999999</v>
       </c>
       <c r="L73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.72737686139748</v>
       </c>
       <c r="M73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>16.824999999999999</v>
       </c>
       <c r="N73" s="63" t="s">
@@ -17689,15 +17647,15 @@
       </c>
       <c r="J74" s="13"/>
       <c r="K74" s="63">
-        <f>D74*25</f>
+        <f t="shared" si="5"/>
         <v>11.600000000000001</v>
       </c>
       <c r="L74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10.775862068965516</v>
       </c>
       <c r="M74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.6000000000000005</v>
       </c>
       <c r="N74" s="63" t="s">
@@ -17731,15 +17689,15 @@
       </c>
       <c r="J75" s="40"/>
       <c r="K75" s="63">
-        <f>D75*25</f>
+        <f t="shared" si="5"/>
         <v>14.674999999999999</v>
       </c>
       <c r="L75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.5178875638841571</v>
       </c>
       <c r="M75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.6749999999999989</v>
       </c>
       <c r="N75" s="63" t="s">
@@ -17754,7 +17712,7 @@
       <c r="B76" s="11">
         <v>53</v>
       </c>
-      <c r="C76" s="108" t="s">
+      <c r="C76" s="13" t="s">
         <v>85</v>
       </c>
       <c r="D76" s="12">
@@ -17775,15 +17733,15 @@
       </c>
       <c r="J76" s="53"/>
       <c r="K76" s="63">
-        <f>D76*25</f>
+        <f t="shared" si="5"/>
         <v>4.8</v>
       </c>
       <c r="L76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3440000000000001</v>
       </c>
       <c r="N76" s="3" t="s">
@@ -17798,7 +17756,7 @@
       <c r="B77" s="11">
         <v>54</v>
       </c>
-      <c r="C77" s="108" t="s">
+      <c r="C77" s="13" t="s">
         <v>94</v>
       </c>
       <c r="D77" s="12">
@@ -17819,15 +17777,15 @@
       </c>
       <c r="J77" s="75"/>
       <c r="K77" s="63">
-        <f>D77*25</f>
+        <f t="shared" si="5"/>
         <v>5.9749999999999996</v>
       </c>
       <c r="L77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.673</v>
       </c>
       <c r="N77" s="3" t="s">
@@ -17842,7 +17800,7 @@
       <c r="B78" s="11">
         <v>55</v>
       </c>
-      <c r="C78" s="110" t="s">
+      <c r="C78" s="15" t="s">
         <v>96</v>
       </c>
       <c r="D78" s="12">
@@ -17863,15 +17821,15 @@
       </c>
       <c r="J78" s="75"/>
       <c r="K78" s="63">
-        <f>D78*25</f>
+        <f t="shared" si="5"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="L78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15.060240963855421</v>
       </c>
       <c r="M78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.3000000000000007</v>
       </c>
       <c r="N78" s="3" t="s">
@@ -17886,7 +17844,7 @@
       <c r="B79" s="13">
         <v>56</v>
       </c>
-      <c r="C79" s="108" t="s">
+      <c r="C79" s="13" t="s">
         <v>98</v>
       </c>
       <c r="D79" s="14">
@@ -17907,15 +17865,15 @@
       </c>
       <c r="J79" s="75"/>
       <c r="K79" s="63">
-        <f>D79*25</f>
+        <f t="shared" si="5"/>
         <v>3.6249999999999996</v>
       </c>
       <c r="L79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0149999999999999</v>
       </c>
       <c r="N79" s="3" t="s">
@@ -17930,7 +17888,7 @@
       <c r="B80" s="13">
         <v>57</v>
       </c>
-      <c r="C80" s="108" t="s">
+      <c r="C80" s="13" t="s">
         <v>100</v>
       </c>
       <c r="D80" s="14">
@@ -17951,15 +17909,15 @@
       </c>
       <c r="J80" s="75"/>
       <c r="K80" s="63">
-        <f>D80*25</f>
+        <f t="shared" si="5"/>
         <v>3.4750000000000005</v>
       </c>
       <c r="L80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.97300000000000009</v>
       </c>
       <c r="N80" s="3" t="s">
@@ -17974,7 +17932,7 @@
       <c r="B81" s="13">
         <v>58</v>
       </c>
-      <c r="C81" s="108" t="s">
+      <c r="C81" s="13" t="s">
         <v>102</v>
       </c>
       <c r="D81" s="14">
@@ -17995,15 +17953,15 @@
       </c>
       <c r="J81" s="75"/>
       <c r="K81" s="63">
-        <f>D81*25</f>
+        <f t="shared" si="5"/>
         <v>2.25</v>
       </c>
       <c r="L81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="N81" s="3" t="s">
@@ -18018,7 +17976,7 @@
       <c r="B82" s="13">
         <v>59</v>
       </c>
-      <c r="C82" s="108" t="s">
+      <c r="C82" s="13" t="s">
         <v>103</v>
       </c>
       <c r="D82" s="14">
@@ -18039,15 +17997,15 @@
       </c>
       <c r="J82" s="75"/>
       <c r="K82" s="63">
-        <f>D82*25</f>
+        <f t="shared" si="5"/>
         <v>2.75</v>
       </c>
       <c r="L82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.77</v>
       </c>
       <c r="N82" s="3" t="s">
@@ -18062,7 +18020,7 @@
       <c r="B83" s="13">
         <v>60</v>
       </c>
-      <c r="C83" s="108" t="s">
+      <c r="C83" s="13" t="s">
         <v>104</v>
       </c>
       <c r="D83" s="12">
@@ -18083,15 +18041,15 @@
       </c>
       <c r="J83" s="75"/>
       <c r="K83" s="63">
-        <f>D83*25</f>
+        <f t="shared" si="5"/>
         <v>6.4249999999999998</v>
       </c>
       <c r="L83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7989999999999999</v>
       </c>
       <c r="N83" s="3" t="s">
@@ -18106,7 +18064,7 @@
       <c r="B84" s="13">
         <v>61</v>
       </c>
-      <c r="C84" s="108" t="s">
+      <c r="C84" s="13" t="s">
         <v>105</v>
       </c>
       <c r="D84" s="14">
@@ -18127,15 +18085,15 @@
       </c>
       <c r="J84" s="75"/>
       <c r="K84" s="63">
-        <f>D84*25</f>
+        <f t="shared" si="5"/>
         <v>2.625</v>
       </c>
       <c r="L84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.73499999999999999</v>
       </c>
       <c r="N84" s="3" t="s">
@@ -18150,7 +18108,7 @@
       <c r="B85" s="13">
         <v>62</v>
       </c>
-      <c r="C85" s="108" t="s">
+      <c r="C85" s="13" t="s">
         <v>106</v>
       </c>
       <c r="D85" s="12">
@@ -18171,15 +18129,15 @@
       </c>
       <c r="J85" s="75"/>
       <c r="K85" s="63">
-        <f>D85*25</f>
+        <f t="shared" si="5"/>
         <v>5.4249999999999998</v>
       </c>
       <c r="L85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5189999999999999</v>
       </c>
       <c r="N85" s="3" t="s">
@@ -18194,7 +18152,7 @@
       <c r="B86" s="13">
         <v>19</v>
       </c>
-      <c r="C86" s="108" t="s">
+      <c r="C86" s="13" t="s">
         <v>173</v>
       </c>
       <c r="D86" s="12" t="s">
@@ -18215,15 +18173,15 @@
       </c>
       <c r="J86" s="75"/>
       <c r="K86" s="63" t="e">
-        <f>D86*25</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="L86" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="M86" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="N86" s="3" t="s">
@@ -18238,7 +18196,7 @@
       <c r="B87" s="13">
         <v>63</v>
       </c>
-      <c r="C87" s="108" t="s">
+      <c r="C87" s="13" t="s">
         <v>108</v>
       </c>
       <c r="D87" s="14">
@@ -18259,15 +18217,15 @@
       </c>
       <c r="J87" s="75"/>
       <c r="K87" s="63">
-        <f>D87*25</f>
+        <f t="shared" si="5"/>
         <v>3.6249999999999996</v>
       </c>
       <c r="L87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0149999999999999</v>
       </c>
       <c r="N87" s="3" t="s">
@@ -18282,7 +18240,7 @@
       <c r="B88" s="13">
         <v>64</v>
       </c>
-      <c r="C88" s="108" t="s">
+      <c r="C88" s="13" t="s">
         <v>109</v>
       </c>
       <c r="D88" s="12">
@@ -18303,15 +18261,15 @@
       </c>
       <c r="J88" s="75"/>
       <c r="K88" s="63">
-        <f>D88*25</f>
+        <f t="shared" si="5"/>
         <v>48.5</v>
       </c>
       <c r="L88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.5773195876288661</v>
       </c>
       <c r="M88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>43.499999999999993</v>
       </c>
       <c r="N88" s="3" t="s">
@@ -18326,7 +18284,7 @@
       <c r="B89" s="11">
         <v>65</v>
       </c>
-      <c r="C89" s="106" t="s">
+      <c r="C89" s="11" t="s">
         <v>110</v>
       </c>
       <c r="D89" s="12">
@@ -18347,15 +18305,15 @@
       </c>
       <c r="J89" s="53"/>
       <c r="K89" s="63">
-        <f>D89*25</f>
+        <f t="shared" si="5"/>
         <v>4.7249999999999996</v>
       </c>
       <c r="L89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.323</v>
       </c>
       <c r="N89" s="3" t="s">
@@ -18370,7 +18328,7 @@
       <c r="B90" s="11">
         <v>66</v>
       </c>
-      <c r="C90" s="106" t="s">
+      <c r="C90" s="11" t="s">
         <v>232</v>
       </c>
       <c r="D90" s="14">
@@ -18391,15 +18349,15 @@
       </c>
       <c r="J90" s="53"/>
       <c r="K90" s="63">
-        <f>D90*25</f>
+        <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
       <c r="L90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="N90" s="3" t="s">
@@ -18414,7 +18372,7 @@
       <c r="B91" s="11">
         <v>67</v>
       </c>
-      <c r="C91" s="106" t="s">
+      <c r="C91" s="11" t="s">
         <v>112</v>
       </c>
       <c r="D91" s="12">
@@ -18435,15 +18393,15 @@
       </c>
       <c r="J91" s="53"/>
       <c r="K91" s="63">
-        <f>D91*25</f>
+        <f t="shared" si="5"/>
         <v>4.1000000000000005</v>
       </c>
       <c r="L91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1480000000000001</v>
       </c>
       <c r="N91" s="3" t="s">
@@ -18458,7 +18416,7 @@
       <c r="B92" s="11">
         <v>68</v>
       </c>
-      <c r="C92" s="106" t="s">
+      <c r="C92" s="11" t="s">
         <v>234</v>
       </c>
       <c r="D92" s="14">
@@ -18479,15 +18437,15 @@
       </c>
       <c r="J92" s="53"/>
       <c r="K92" s="63">
-        <f>D92*25</f>
+        <f t="shared" si="5"/>
         <v>2.7250000000000001</v>
       </c>
       <c r="L92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.76300000000000001</v>
       </c>
       <c r="N92" s="3" t="s">
@@ -18502,7 +18460,7 @@
       <c r="B93" s="11">
         <v>49</v>
       </c>
-      <c r="C93" s="106" t="s">
+      <c r="C93" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D93" s="12">
@@ -18525,15 +18483,15 @@
         <v>236</v>
       </c>
       <c r="K93" s="63">
-        <f>D93*25</f>
+        <f t="shared" si="5"/>
         <v>6.7750000000000004</v>
       </c>
       <c r="L93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8970000000000002</v>
       </c>
       <c r="N93" s="3" t="s">
@@ -18548,7 +18506,7 @@
       <c r="B94" s="11">
         <v>50</v>
       </c>
-      <c r="C94" s="106" t="s">
+      <c r="C94" s="11" t="s">
         <v>237</v>
       </c>
       <c r="D94" s="12">
@@ -18571,15 +18529,15 @@
         <v>236</v>
       </c>
       <c r="K94" s="63">
-        <f>D94*25</f>
+        <f t="shared" si="5"/>
         <v>6.5250000000000004</v>
       </c>
       <c r="L94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.827</v>
       </c>
       <c r="N94" s="3" t="s">
@@ -18594,7 +18552,7 @@
       <c r="B95" s="13">
         <v>51</v>
       </c>
-      <c r="C95" s="106" t="s">
+      <c r="C95" s="11" t="s">
         <v>238</v>
       </c>
       <c r="D95" s="12">
@@ -18617,15 +18575,15 @@
         <v>236</v>
       </c>
       <c r="K95" s="63">
-        <f>D95*25</f>
+        <f t="shared" si="5"/>
         <v>5.65</v>
       </c>
       <c r="L95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5820000000000001</v>
       </c>
       <c r="N95" s="3" t="s">
@@ -18640,7 +18598,7 @@
       <c r="B96" s="13">
         <v>52</v>
       </c>
-      <c r="C96" s="106" t="s">
+      <c r="C96" s="11" t="s">
         <v>239</v>
       </c>
       <c r="D96" s="12">
@@ -18663,15 +18621,15 @@
         <v>236</v>
       </c>
       <c r="K96" s="63">
-        <f>D96*25</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="L96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="N96" s="3" t="s">
@@ -18686,7 +18644,7 @@
       <c r="B97" s="13">
         <v>73</v>
       </c>
-      <c r="C97" s="111" t="s">
+      <c r="C97" s="106" t="s">
         <v>116</v>
       </c>
       <c r="D97" s="12">
@@ -18707,15 +18665,15 @@
       </c>
       <c r="J97" s="53"/>
       <c r="K97" s="63">
-        <f>D97*25</f>
+        <f t="shared" si="5"/>
         <v>3.75</v>
       </c>
       <c r="L97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.05</v>
       </c>
       <c r="N97" s="3" t="s">
@@ -18730,7 +18688,7 @@
       <c r="B98" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="C98" s="112" t="s">
+      <c r="C98" s="12" t="s">
         <v>116</v>
       </c>
       <c r="D98" s="12">
@@ -18753,15 +18711,15 @@
       </c>
       <c r="J98" s="40"/>
       <c r="K98" s="63">
-        <f>D98*25</f>
+        <f t="shared" ref="K98:K129" si="7">D98*25</f>
         <v>3.1749999999999998</v>
       </c>
       <c r="L98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.88900000000000001</v>
       </c>
       <c r="N98" s="3" t="s">
@@ -18776,7 +18734,7 @@
       <c r="B99" s="13">
         <v>74</v>
       </c>
-      <c r="C99" s="111" t="s">
+      <c r="C99" s="106" t="s">
         <v>242</v>
       </c>
       <c r="D99" s="12">
@@ -18797,15 +18755,15 @@
       </c>
       <c r="J99" s="40"/>
       <c r="K99" s="63">
-        <f>D99*25</f>
+        <f t="shared" si="7"/>
         <v>3.8249999999999997</v>
       </c>
       <c r="L99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.071</v>
       </c>
       <c r="N99" s="3" t="s">
@@ -18820,7 +18778,7 @@
       <c r="B100" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="C100" s="113" t="s">
+      <c r="C100" s="107" t="s">
         <v>118</v>
       </c>
       <c r="D100" s="12">
@@ -18843,15 +18801,15 @@
       </c>
       <c r="J100" s="40"/>
       <c r="K100" s="63">
-        <f>D100*25</f>
+        <f t="shared" si="7"/>
         <v>3.6749999999999998</v>
       </c>
       <c r="L100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0289999999999999</v>
       </c>
       <c r="N100" s="3" t="s">
@@ -18866,7 +18824,7 @@
       <c r="B101" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C101" s="113" t="s">
+      <c r="C101" s="107" t="s">
         <v>118</v>
       </c>
       <c r="D101" s="12">
@@ -18889,15 +18847,15 @@
       </c>
       <c r="J101" s="40"/>
       <c r="K101" s="63">
-        <f>D101*25</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="L101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1200000000000001</v>
       </c>
       <c r="N101" s="3" t="s">
@@ -18912,7 +18870,7 @@
       <c r="B102" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="C102" s="113" t="s">
+      <c r="C102" s="107" t="s">
         <v>120</v>
       </c>
       <c r="D102" s="12">
@@ -18935,15 +18893,15 @@
       </c>
       <c r="J102" s="40"/>
       <c r="K102" s="63">
-        <f>D102*25</f>
+        <f t="shared" si="7"/>
         <v>4.0250000000000004</v>
       </c>
       <c r="L102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.127</v>
       </c>
       <c r="N102" s="3" t="s">
@@ -18958,7 +18916,7 @@
       <c r="B103" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C103" s="114" t="s">
+      <c r="C103" s="108" t="s">
         <v>120</v>
       </c>
       <c r="D103" s="34">
@@ -18981,15 +18939,15 @@
       </c>
       <c r="J103" s="56"/>
       <c r="K103" s="63">
-        <f>D103*25</f>
+        <f t="shared" si="7"/>
         <v>6.05</v>
       </c>
       <c r="L103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M103">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.694</v>
       </c>
       <c r="N103" s="3" t="s">
@@ -19004,7 +18962,7 @@
       <c r="B104" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C104" s="112" t="s">
+      <c r="C104" s="12" t="s">
         <v>121</v>
       </c>
       <c r="D104" s="12">
@@ -19027,15 +18985,15 @@
       </c>
       <c r="J104" s="40"/>
       <c r="K104" s="63">
-        <f>D104*25</f>
+        <f t="shared" si="7"/>
         <v>5.55</v>
       </c>
       <c r="L104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.554</v>
       </c>
       <c r="N104" s="3" t="s">
@@ -19050,7 +19008,7 @@
       <c r="B105" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C105" s="112" t="s">
+      <c r="C105" s="12" t="s">
         <v>121</v>
       </c>
       <c r="D105" s="12">
@@ -19073,15 +19031,15 @@
       </c>
       <c r="J105" s="40"/>
       <c r="K105" s="63">
-        <f>D105*25</f>
+        <f t="shared" si="7"/>
         <v>6.3</v>
       </c>
       <c r="L105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.764</v>
       </c>
       <c r="N105" s="3" t="s">
@@ -19096,7 +19054,7 @@
       <c r="B106" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C106" s="112" t="s">
+      <c r="C106" s="12" t="s">
         <v>123</v>
       </c>
       <c r="D106" s="12">
@@ -19119,15 +19077,15 @@
       </c>
       <c r="J106" s="40"/>
       <c r="K106" s="63">
-        <f>D106*25</f>
+        <f t="shared" si="7"/>
         <v>4.875</v>
       </c>
       <c r="L106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M106">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.365</v>
       </c>
       <c r="N106" s="3" t="s">
@@ -19142,7 +19100,7 @@
       <c r="B107" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="C107" s="112" t="s">
+      <c r="C107" s="12" t="s">
         <v>123</v>
       </c>
       <c r="D107" s="12">
@@ -19165,15 +19123,15 @@
       </c>
       <c r="J107" s="40"/>
       <c r="K107" s="63">
-        <f>D107*25</f>
+        <f t="shared" si="7"/>
         <v>5.4</v>
       </c>
       <c r="L107">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.512</v>
       </c>
       <c r="N107" s="3" t="s">
@@ -19188,7 +19146,7 @@
       <c r="B108" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C108" s="112" t="s">
+      <c r="C108" s="12" t="s">
         <v>124</v>
       </c>
       <c r="D108" s="69">
@@ -19211,15 +19169,15 @@
       </c>
       <c r="J108" s="40"/>
       <c r="K108" s="63">
-        <f>D108*25</f>
+        <f t="shared" si="7"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="L108">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M108">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4279999999999999</v>
       </c>
       <c r="N108" s="3" t="s">
@@ -19234,7 +19192,7 @@
       <c r="B109" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C109" s="112" t="s">
+      <c r="C109" s="12" t="s">
         <v>124</v>
       </c>
       <c r="D109" s="12">
@@ -19257,15 +19215,15 @@
       </c>
       <c r="J109" s="40"/>
       <c r="K109" s="63">
-        <f>D109*25</f>
+        <f t="shared" si="7"/>
         <v>5.875</v>
       </c>
       <c r="L109">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.645</v>
       </c>
       <c r="N109" s="3" t="s">
@@ -19280,7 +19238,7 @@
       <c r="B110" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="C110" s="106" t="s">
+      <c r="C110" s="11" t="s">
         <v>125</v>
       </c>
       <c r="D110" s="12">
@@ -19303,15 +19261,15 @@
       </c>
       <c r="J110" s="40"/>
       <c r="K110" s="63">
-        <f>D110*25</f>
+        <f t="shared" si="7"/>
         <v>2.7749999999999999</v>
       </c>
       <c r="L110">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.77700000000000002</v>
       </c>
       <c r="N110" s="3" t="s">
@@ -19326,7 +19284,7 @@
       <c r="B111" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C111" s="106" t="s">
+      <c r="C111" s="11" t="s">
         <v>125</v>
       </c>
       <c r="D111" s="12">
@@ -19349,15 +19307,15 @@
       </c>
       <c r="J111" s="40"/>
       <c r="K111" s="63">
-        <f>D111*25</f>
+        <f t="shared" si="7"/>
         <v>3.65</v>
       </c>
       <c r="L111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M111">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.022</v>
       </c>
       <c r="N111" s="3" t="s">
@@ -19372,7 +19330,7 @@
       <c r="B112" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C112" s="106" t="s">
+      <c r="C112" s="11" t="s">
         <v>127</v>
       </c>
       <c r="D112" s="12">
@@ -19395,15 +19353,15 @@
       </c>
       <c r="J112" s="40"/>
       <c r="K112" s="63">
-        <f>D112*25</f>
+        <f t="shared" si="7"/>
         <v>4.8</v>
       </c>
       <c r="L112">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M112">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3440000000000001</v>
       </c>
       <c r="N112" s="3" t="s">
@@ -19441,15 +19399,15 @@
       </c>
       <c r="J113" s="40"/>
       <c r="K113" s="63">
-        <f>D113*25</f>
+        <f t="shared" si="7"/>
         <v>7.7249999999999996</v>
       </c>
       <c r="L113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16.181229773462782</v>
       </c>
       <c r="M113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.7250000000000005</v>
       </c>
       <c r="N113" s="3" t="s">
@@ -19489,15 +19447,15 @@
       </c>
       <c r="J114" s="40"/>
       <c r="K114" s="63">
-        <f>D114*25</f>
+        <f t="shared" si="7"/>
         <v>7.3</v>
       </c>
       <c r="L114">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17.123287671232877</v>
       </c>
       <c r="M114">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="N114" s="3" t="s">
@@ -19514,7 +19472,7 @@
       <c r="B115" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="C115" s="112" t="s">
+      <c r="C115" s="12" t="s">
         <v>128</v>
       </c>
       <c r="D115" s="12">
@@ -19537,15 +19495,15 @@
       </c>
       <c r="J115" s="40"/>
       <c r="K115" s="63">
-        <f>D115*25</f>
+        <f t="shared" si="7"/>
         <v>6.5250000000000004</v>
       </c>
       <c r="L115">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M115">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.827</v>
       </c>
       <c r="N115" s="3" t="s">
@@ -19585,15 +19543,15 @@
       </c>
       <c r="J116" s="40"/>
       <c r="K116" s="63">
-        <f>D116*25</f>
+        <f t="shared" si="7"/>
         <v>7.55</v>
       </c>
       <c r="L116">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16.556291390728479</v>
       </c>
       <c r="M116">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.5499999999999994</v>
       </c>
       <c r="N116" s="3" t="s">
@@ -19633,15 +19591,15 @@
       </c>
       <c r="J117" s="40"/>
       <c r="K117" s="63">
-        <f>D117*25</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="L117">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>13.888888888888889</v>
       </c>
       <c r="M117">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.9999999999999996</v>
       </c>
       <c r="N117" s="3" t="s">
@@ -19656,7 +19614,7 @@
       <c r="B118" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="C118" s="115" t="s">
+      <c r="C118" s="17" t="s">
         <v>131</v>
       </c>
       <c r="D118" s="12">
@@ -19679,15 +19637,15 @@
       </c>
       <c r="J118" s="40"/>
       <c r="K118" s="63">
-        <f>D118*25</f>
+        <f t="shared" si="7"/>
         <v>4.6749999999999998</v>
       </c>
       <c r="L118">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M118">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3089999999999999</v>
       </c>
       <c r="N118" s="3" t="s">
@@ -19702,7 +19660,7 @@
       <c r="B119" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="C119" s="115" t="s">
+      <c r="C119" s="17" t="s">
         <v>131</v>
       </c>
       <c r="D119" s="23">
@@ -19725,15 +19683,15 @@
       </c>
       <c r="J119" s="40"/>
       <c r="K119" s="63">
-        <f>D119*25</f>
+        <f t="shared" si="7"/>
         <v>4.05</v>
       </c>
       <c r="L119">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M119">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1340000000000001</v>
       </c>
       <c r="N119" s="3" t="s">
@@ -19773,15 +19731,15 @@
       </c>
       <c r="J120" s="40"/>
       <c r="K120" s="63">
-        <f>D120*25</f>
+        <f t="shared" si="7"/>
         <v>7.0250000000000004</v>
       </c>
       <c r="L120">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17.793594306049819</v>
       </c>
       <c r="M120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0250000000000012</v>
       </c>
       <c r="N120" s="3" t="s">
@@ -19821,15 +19779,15 @@
       </c>
       <c r="J121" s="40"/>
       <c r="K121" s="63">
-        <f>D121*25</f>
+        <f t="shared" si="7"/>
         <v>7.3999999999999995</v>
       </c>
       <c r="L121">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16.891891891891891</v>
       </c>
       <c r="M121">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.4</v>
       </c>
       <c r="N121" s="3" t="s">
@@ -19846,7 +19804,7 @@
       <c r="B122" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C122" s="108" t="s">
+      <c r="C122" s="13" t="s">
         <v>136</v>
       </c>
       <c r="D122" s="12">
@@ -19869,15 +19827,15 @@
       </c>
       <c r="J122" s="40"/>
       <c r="K122" s="63">
-        <f>D122*25</f>
+        <f t="shared" si="7"/>
         <v>6.9</v>
       </c>
       <c r="L122">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M122">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9320000000000002</v>
       </c>
       <c r="N122" s="3" t="s">
@@ -19894,7 +19852,7 @@
       <c r="B123" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C123" s="108" t="s">
+      <c r="C123" s="13" t="s">
         <v>136</v>
       </c>
       <c r="D123" s="12">
@@ -19917,15 +19875,15 @@
       </c>
       <c r="J123" s="40"/>
       <c r="K123" s="63">
-        <f>D123*25</f>
+        <f t="shared" si="7"/>
         <v>6.9250000000000007</v>
       </c>
       <c r="L123">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M123">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9390000000000001</v>
       </c>
       <c r="N123" s="3" t="s">
@@ -19942,7 +19900,7 @@
       <c r="B124" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C124" s="108" t="s">
+      <c r="C124" s="13" t="s">
         <v>137</v>
       </c>
       <c r="D124" s="34">
@@ -19965,15 +19923,15 @@
       </c>
       <c r="J124" s="13"/>
       <c r="K124" s="63">
-        <f>D124*25</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
       <c r="L124">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M124">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.47</v>
       </c>
       <c r="N124" s="3" t="s">
@@ -19990,7 +19948,7 @@
       <c r="B125" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="C125" s="108" t="s">
+      <c r="C125" s="13" t="s">
         <v>137</v>
       </c>
       <c r="D125" s="12">
@@ -20013,15 +19971,15 @@
       </c>
       <c r="J125" s="13"/>
       <c r="K125" s="63">
-        <f>D125*25</f>
+        <f t="shared" si="7"/>
         <v>5.5250000000000004</v>
       </c>
       <c r="L125">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M125">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5469999999999999</v>
       </c>
       <c r="N125" s="3" t="s">
@@ -20038,7 +19996,7 @@
       <c r="B126" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="C126" s="106" t="s">
+      <c r="C126" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D126" s="12">
@@ -20061,15 +20019,15 @@
       </c>
       <c r="J126" s="13"/>
       <c r="K126" s="63">
-        <f>D126*25</f>
+        <f t="shared" si="7"/>
         <v>5.6749999999999998</v>
       </c>
       <c r="L126">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M126">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.589</v>
       </c>
       <c r="N126" s="3" t="s">
@@ -20086,7 +20044,7 @@
       <c r="B127" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C127" s="106" t="s">
+      <c r="C127" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D127" s="12">
@@ -20109,15 +20067,15 @@
       </c>
       <c r="J127" s="13"/>
       <c r="K127" s="63">
-        <f>D127*25</f>
+        <f t="shared" si="7"/>
         <v>6.0750000000000002</v>
       </c>
       <c r="L127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M127">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7010000000000001</v>
       </c>
       <c r="N127" s="3" t="s">
@@ -20132,7 +20090,7 @@
       <c r="B128" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="C128" s="106" t="s">
+      <c r="C128" s="11" t="s">
         <v>139</v>
       </c>
       <c r="D128" s="12">
@@ -20153,15 +20111,15 @@
       </c>
       <c r="J128" s="40"/>
       <c r="K128" s="63">
-        <f>D128*25</f>
+        <f t="shared" si="7"/>
         <v>3.7749999999999999</v>
       </c>
       <c r="L128">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M128">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0569999999999999</v>
       </c>
       <c r="N128" s="3" t="s">
@@ -20176,7 +20134,7 @@
       <c r="B129" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C129" s="106" t="s">
+      <c r="C129" s="11" t="s">
         <v>139</v>
       </c>
       <c r="D129" s="12">
@@ -20197,15 +20155,15 @@
       </c>
       <c r="J129" s="40"/>
       <c r="K129" s="63">
-        <f>D129*25</f>
+        <f t="shared" si="7"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="L129">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="M129">
-        <f t="shared" ref="M129:M190" si="4">(25-L129)*D129</f>
+        <f t="shared" ref="M129:M190" si="8">(25-L129)*D129</f>
         <v>0.92400000000000004</v>
       </c>
       <c r="N129" s="3" t="s">
@@ -20220,7 +20178,7 @@
       <c r="B130" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="C130" s="106" t="s">
+      <c r="C130" s="11" t="s">
         <v>140</v>
       </c>
       <c r="D130" s="32">
@@ -20241,15 +20199,15 @@
       </c>
       <c r="J130" s="40"/>
       <c r="K130" s="63">
-        <f>D130*25</f>
+        <f t="shared" ref="K130:K161" si="9">D130*25</f>
         <v>6.45</v>
       </c>
       <c r="L130">
-        <f t="shared" ref="L130:L191" si="5">IF(5/D130&gt;18,18,5/D130)</f>
+        <f t="shared" ref="L130:L191" si="10">IF(5/D130&gt;18,18,5/D130)</f>
         <v>18</v>
       </c>
       <c r="M130">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.806</v>
       </c>
       <c r="N130" s="3" t="s">
@@ -20289,15 +20247,15 @@
         <v>298</v>
       </c>
       <c r="K131" s="63">
-        <f>D131*25</f>
+        <f t="shared" si="9"/>
         <v>15.725</v>
       </c>
       <c r="L131">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.9491255961844196</v>
       </c>
       <c r="M131">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>10.725</v>
       </c>
       <c r="N131" s="3" t="s">
@@ -20337,15 +20295,15 @@
         <v>298</v>
       </c>
       <c r="K132" s="63">
-        <f>D132*25</f>
+        <f t="shared" si="9"/>
         <v>11.375</v>
       </c>
       <c r="L132">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>10.989010989010989</v>
       </c>
       <c r="M132">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.375</v>
       </c>
       <c r="N132" s="3" t="s">
@@ -20360,7 +20318,7 @@
       <c r="B133" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="C133" s="106" t="s">
+      <c r="C133" s="11" t="s">
         <v>145</v>
       </c>
       <c r="D133" s="12">
@@ -20385,15 +20343,15 @@
         <v>298</v>
       </c>
       <c r="K133" s="63">
-        <f>D133*25</f>
+        <f t="shared" si="9"/>
         <v>4.875</v>
       </c>
       <c r="L133">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="M133">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.365</v>
       </c>
       <c r="N133" s="3" t="s">
@@ -20429,15 +20387,15 @@
       </c>
       <c r="J134" s="40"/>
       <c r="K134" s="63">
-        <f>D134*25</f>
+        <f t="shared" si="9"/>
         <v>19.024999999999999</v>
       </c>
       <c r="L134">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>6.5703022339027592</v>
       </c>
       <c r="M134">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>14.025</v>
       </c>
       <c r="N134" s="3" t="s">
@@ -20473,15 +20431,15 @@
       </c>
       <c r="J135" s="40"/>
       <c r="K135" s="63">
-        <f>D135*25</f>
+        <f t="shared" si="9"/>
         <v>8.5</v>
       </c>
       <c r="L135">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>14.705882352941176</v>
       </c>
       <c r="M135">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.5000000000000004</v>
       </c>
       <c r="N135" s="3" t="s">
@@ -20517,15 +20475,15 @@
       </c>
       <c r="J136" s="40"/>
       <c r="K136" s="63">
-        <f>D136*25</f>
+        <f t="shared" si="9"/>
         <v>7.95</v>
       </c>
       <c r="L136">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.723270440251572</v>
       </c>
       <c r="M136">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.95</v>
       </c>
       <c r="N136" s="3" t="s">
@@ -20561,15 +20519,15 @@
       </c>
       <c r="J137" s="40"/>
       <c r="K137" s="63">
-        <f>D137*25</f>
+        <f t="shared" si="9"/>
         <v>16.074999999999999</v>
       </c>
       <c r="L137">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.7760497667185069</v>
       </c>
       <c r="M137">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>11.074999999999999</v>
       </c>
       <c r="N137" s="3" t="s">
@@ -20605,15 +20563,15 @@
       </c>
       <c r="J138" s="40"/>
       <c r="K138" s="63">
-        <f>D138*25</f>
+        <f t="shared" si="9"/>
         <v>15.2</v>
       </c>
       <c r="L138">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>8.2236842105263168</v>
       </c>
       <c r="M138">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>10.200000000000001</v>
       </c>
       <c r="N138" s="3" t="s">
@@ -20651,15 +20609,15 @@
       </c>
       <c r="J139" s="13"/>
       <c r="K139" s="63">
-        <f>D139*25</f>
+        <f t="shared" si="9"/>
         <v>17.349999999999998</v>
       </c>
       <c r="L139">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.2046109510086458</v>
       </c>
       <c r="M139">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>12.349999999999998</v>
       </c>
       <c r="N139" s="3" t="s">
@@ -20697,15 +20655,15 @@
       </c>
       <c r="J140" s="13"/>
       <c r="K140" s="63">
-        <f>D140*25</f>
+        <f t="shared" si="9"/>
         <v>45.25</v>
       </c>
       <c r="L140">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.7624309392265194</v>
       </c>
       <c r="M140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>40.25</v>
       </c>
       <c r="N140" s="3" t="s">
@@ -20743,15 +20701,15 @@
       </c>
       <c r="J141" s="40"/>
       <c r="K141" s="63">
-        <f>D141*25</f>
+        <f t="shared" si="9"/>
         <v>16.875</v>
       </c>
       <c r="L141">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.4074074074074066</v>
       </c>
       <c r="M141">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>11.875000000000002</v>
       </c>
       <c r="N141" s="3" t="s">
@@ -20789,15 +20747,15 @@
       </c>
       <c r="J142" s="40"/>
       <c r="K142" s="63">
-        <f>D142*25</f>
+        <f t="shared" si="9"/>
         <v>13.375</v>
       </c>
       <c r="L142">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>9.3457943925233646</v>
       </c>
       <c r="M142">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>8.375</v>
       </c>
       <c r="N142" s="3" t="s">
@@ -20835,15 +20793,15 @@
       </c>
       <c r="J143" s="58"/>
       <c r="K143" s="63">
-        <f>D143*25</f>
+        <f t="shared" si="9"/>
         <v>7.7249999999999996</v>
       </c>
       <c r="L143">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>16.181229773462782</v>
       </c>
       <c r="M143">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7250000000000005</v>
       </c>
       <c r="N143" s="3" t="s">
@@ -20881,15 +20839,15 @@
       </c>
       <c r="J144" s="58"/>
       <c r="K144" s="63">
-        <f>D144*25</f>
+        <f t="shared" si="9"/>
         <v>12.3</v>
       </c>
       <c r="L144">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>10.16260162601626</v>
       </c>
       <c r="M144">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7.3</v>
       </c>
       <c r="N144" s="3" t="s">
@@ -20927,15 +20885,15 @@
       </c>
       <c r="J145" s="59"/>
       <c r="K145" s="63">
-        <f>D145*25</f>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="L145">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.166666666666667</v>
       </c>
       <c r="M145">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>24.999999999999996</v>
       </c>
       <c r="N145" s="3" t="s">
@@ -20950,7 +20908,7 @@
       <c r="B146" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="C146" s="110" t="s">
+      <c r="C146" s="15" t="s">
         <v>156</v>
       </c>
       <c r="D146" s="12">
@@ -20973,15 +20931,15 @@
       </c>
       <c r="J146" s="59"/>
       <c r="K146" s="63">
-        <f>D146*25</f>
+        <f t="shared" si="9"/>
         <v>6.8250000000000002</v>
       </c>
       <c r="L146">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="M146">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.911</v>
       </c>
       <c r="N146" s="3" t="s">
@@ -21019,15 +20977,15 @@
       </c>
       <c r="J147" s="59"/>
       <c r="K147" s="63">
-        <f>D147*25</f>
+        <f t="shared" si="9"/>
         <v>17.5</v>
       </c>
       <c r="L147">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.1428571428571432</v>
       </c>
       <c r="M147">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>12.5</v>
       </c>
       <c r="N147" s="3" t="s">
@@ -21065,15 +21023,15 @@
       </c>
       <c r="J148" s="58"/>
       <c r="K148" s="63">
-        <f>D148*25</f>
+        <f t="shared" si="9"/>
         <v>39.5</v>
       </c>
       <c r="L148">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.1645569620253164</v>
       </c>
       <c r="M148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>34.5</v>
       </c>
       <c r="N148" s="3" t="s">
@@ -21111,15 +21069,15 @@
       </c>
       <c r="J149" s="13"/>
       <c r="K149" s="63">
-        <f>D149*25</f>
+        <f t="shared" si="9"/>
         <v>14.574999999999999</v>
       </c>
       <c r="L149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>8.5763293310463133</v>
       </c>
       <c r="M149">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>9.5749999999999993</v>
       </c>
       <c r="N149" s="3" t="s">
@@ -21157,15 +21115,15 @@
       </c>
       <c r="J150" s="13"/>
       <c r="K150" s="63">
-        <f>D150*25</f>
+        <f t="shared" si="9"/>
         <v>12.025</v>
       </c>
       <c r="L150">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>10.395010395010395</v>
       </c>
       <c r="M150">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7.0249999999999995</v>
       </c>
       <c r="N150" s="3" t="s">
@@ -21203,15 +21161,15 @@
         <v>26.5</v>
       </c>
       <c r="K151" s="63">
-        <f>D151*25</f>
+        <f t="shared" si="9"/>
         <v>26.5</v>
       </c>
       <c r="L151">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.7169811320754711</v>
       </c>
       <c r="M151">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>21.5</v>
       </c>
       <c r="N151" s="3" t="s">
@@ -21249,15 +21207,15 @@
         <v>23.95</v>
       </c>
       <c r="K152" s="63">
-        <f>D152*25</f>
+        <f t="shared" si="9"/>
         <v>23.95</v>
       </c>
       <c r="L152">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.2192066805845512</v>
       </c>
       <c r="M152">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>18.95</v>
       </c>
       <c r="N152" s="3" t="s">
@@ -21295,15 +21253,15 @@
         <v>8.35</v>
       </c>
       <c r="K153" s="63">
-        <f>D153*25</f>
+        <f t="shared" si="9"/>
         <v>8.35</v>
       </c>
       <c r="L153">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>14.97005988023952</v>
       </c>
       <c r="M153">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.3500000000000005</v>
       </c>
       <c r="N153" s="3" t="s">
@@ -21341,15 +21299,15 @@
         <v>24.975000000000001</v>
       </c>
       <c r="K154" s="63">
-        <f>D154*25</f>
+        <f t="shared" si="9"/>
         <v>24.975000000000001</v>
       </c>
       <c r="L154">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.005005005005005</v>
       </c>
       <c r="M154">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>19.975000000000001</v>
       </c>
       <c r="N154" s="3" t="s">
@@ -21385,15 +21343,15 @@
       </c>
       <c r="J155" s="40"/>
       <c r="K155" s="63">
-        <f>D155*25</f>
+        <f t="shared" si="9"/>
         <v>16.950000000000003</v>
       </c>
       <c r="L155">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.3746312684365778</v>
       </c>
       <c r="M155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>11.950000000000001</v>
       </c>
       <c r="N155" s="3" t="s">
@@ -21429,15 +21387,15 @@
       </c>
       <c r="J156" s="13"/>
       <c r="K156" s="63">
-        <f>D156*25</f>
+        <f t="shared" si="9"/>
         <v>8.3250000000000011</v>
       </c>
       <c r="L156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.015015015015015</v>
       </c>
       <c r="M156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.3250000000000002</v>
       </c>
       <c r="N156" s="3" t="s">
@@ -21473,15 +21431,15 @@
       </c>
       <c r="J157" s="13"/>
       <c r="K157" s="63">
-        <f>D157*25</f>
+        <f t="shared" si="9"/>
         <v>12.85</v>
       </c>
       <c r="L157">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>9.7276264591439681</v>
       </c>
       <c r="M157">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7.8500000000000005</v>
       </c>
       <c r="N157" s="3" t="s">
@@ -21517,15 +21475,15 @@
       </c>
       <c r="J158" s="40"/>
       <c r="K158" s="63">
-        <f>D158*25</f>
+        <f t="shared" si="9"/>
         <v>14.75</v>
       </c>
       <c r="L158">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>8.4745762711864412</v>
       </c>
       <c r="M158">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>9.7499999999999982</v>
       </c>
       <c r="N158" s="3" t="s">
@@ -21563,15 +21521,15 @@
       </c>
       <c r="J159" s="76"/>
       <c r="K159" s="63">
-        <f>D159*25</f>
+        <f t="shared" si="9"/>
         <v>47</v>
       </c>
       <c r="L159">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.6595744680851063</v>
       </c>
       <c r="M159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>41.999999999999993</v>
       </c>
       <c r="N159" s="3" t="s">
@@ -21609,15 +21567,15 @@
       </c>
       <c r="J160" s="61"/>
       <c r="K160" s="63">
-        <f>D160*25</f>
+        <f t="shared" si="9"/>
         <v>8.9</v>
       </c>
       <c r="L160">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>14.04494382022472</v>
       </c>
       <c r="M160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.8999999999999995</v>
       </c>
       <c r="N160" s="3" t="s">
@@ -21653,15 +21611,15 @@
       </c>
       <c r="J161" s="40"/>
       <c r="K161" s="63">
-        <f>D161*25</f>
+        <f t="shared" si="9"/>
         <v>18.45</v>
       </c>
       <c r="L161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>6.7750677506775068</v>
       </c>
       <c r="M161">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>13.45</v>
       </c>
       <c r="N161" s="3" t="s">
@@ -21697,15 +21655,15 @@
       </c>
       <c r="J162" s="40"/>
       <c r="K162" s="63">
-        <f>D162*25</f>
+        <f t="shared" ref="K162:K195" si="11">D162*25</f>
         <v>29.75</v>
       </c>
       <c r="L162">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.2016806722689077</v>
       </c>
       <c r="M162">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>24.75</v>
       </c>
       <c r="N162" s="3" t="s">
@@ -21743,15 +21701,15 @@
       </c>
       <c r="J163" s="13"/>
       <c r="K163" s="63">
-        <f>D163*25</f>
+        <f t="shared" si="11"/>
         <v>9.9250000000000007</v>
       </c>
       <c r="L163">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>12.594458438287154</v>
       </c>
       <c r="M163">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>4.9249999999999998</v>
       </c>
       <c r="N163" s="3" t="s">
@@ -21789,15 +21747,15 @@
       </c>
       <c r="J164" s="13"/>
       <c r="K164" s="63">
-        <f>D164*25</f>
+        <f t="shared" si="11"/>
         <v>118.5</v>
       </c>
       <c r="L164">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.0548523206751055</v>
       </c>
       <c r="M164">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>113.5</v>
       </c>
       <c r="N164" s="3" t="s">
@@ -21833,15 +21791,15 @@
       </c>
       <c r="J165" s="13"/>
       <c r="K165" s="63">
-        <f>D165*25</f>
+        <f t="shared" si="11"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="L165">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>14.367816091954024</v>
       </c>
       <c r="M165">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.6999999999999993</v>
       </c>
       <c r="N165" s="3" t="s">
@@ -21877,15 +21835,15 @@
       </c>
       <c r="J166" s="13"/>
       <c r="K166" s="63">
-        <f>D166*25</f>
+        <f t="shared" si="11"/>
         <v>11.875</v>
       </c>
       <c r="L166">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>10.526315789473685</v>
       </c>
       <c r="M166">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.8749999999999991</v>
       </c>
       <c r="N166" s="3" t="s">
@@ -21923,15 +21881,15 @@
       </c>
       <c r="J167" s="13"/>
       <c r="K167" s="63">
-        <f>D167*25</f>
+        <f t="shared" si="11"/>
         <v>10.824999999999999</v>
       </c>
       <c r="L167">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>11.547344110854503</v>
       </c>
       <c r="M167">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.8250000000000002</v>
       </c>
       <c r="N167" s="3" t="s">
@@ -21969,15 +21927,15 @@
       </c>
       <c r="J168" s="13"/>
       <c r="K168" s="63">
-        <f>D168*25</f>
+        <f t="shared" si="11"/>
         <v>8.7749999999999986</v>
       </c>
       <c r="L168">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>14.245014245014247</v>
       </c>
       <c r="M168">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.7749999999999995</v>
       </c>
       <c r="N168" s="3" t="s">
@@ -22015,15 +21973,15 @@
       </c>
       <c r="J169" s="13"/>
       <c r="K169" s="63">
-        <f>D169*25</f>
+        <f t="shared" si="11"/>
         <v>20.925000000000001</v>
       </c>
       <c r="L169">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.9737156511350058</v>
       </c>
       <c r="M169">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>15.924999999999999</v>
       </c>
       <c r="N169" s="3" t="s">
@@ -22057,15 +22015,15 @@
       </c>
       <c r="J170" s="40"/>
       <c r="K170" s="63">
-        <f>D170*25</f>
+        <f t="shared" si="11"/>
         <v>33.5</v>
       </c>
       <c r="L170">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.7313432835820892</v>
       </c>
       <c r="M170">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>28.500000000000004</v>
       </c>
       <c r="N170" s="3" t="s">
@@ -22099,15 +22057,15 @@
       </c>
       <c r="J171" s="40"/>
       <c r="K171" s="63">
-        <f>D171*25</f>
+        <f t="shared" si="11"/>
         <v>10.7</v>
       </c>
       <c r="L171">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>11.682242990654206</v>
       </c>
       <c r="M171">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.6999999999999993</v>
       </c>
       <c r="N171" s="3" t="s">
@@ -22141,15 +22099,15 @@
       </c>
       <c r="J172" s="40"/>
       <c r="K172" s="63">
-        <f>D172*25</f>
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
       <c r="L172">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.3783783783783785</v>
       </c>
       <c r="M172">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="N172" s="3" t="s">
@@ -22183,15 +22141,15 @@
       </c>
       <c r="J173" s="40"/>
       <c r="K173" s="63">
-        <f>D173*25</f>
+        <f t="shared" si="11"/>
         <v>10.025</v>
       </c>
       <c r="L173">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>12.468827930174562</v>
       </c>
       <c r="M173">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.0250000000000004</v>
       </c>
       <c r="N173" s="3" t="s">
@@ -22225,15 +22183,15 @@
       </c>
       <c r="J174" s="40"/>
       <c r="K174" s="63">
-        <f>D174*25</f>
+        <f t="shared" si="11"/>
         <v>8.8249999999999993</v>
       </c>
       <c r="L174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>14.164305949008499</v>
       </c>
       <c r="M174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3.8249999999999997</v>
       </c>
       <c r="N174" s="3" t="s">
@@ -22267,15 +22225,15 @@
       </c>
       <c r="J175" s="40"/>
       <c r="K175" s="63">
-        <f>D175*25</f>
+        <f t="shared" si="11"/>
         <v>16.875</v>
       </c>
       <c r="L175">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.4074074074074066</v>
       </c>
       <c r="M175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>11.875000000000002</v>
       </c>
       <c r="N175" s="3" t="s">
@@ -22309,15 +22267,15 @@
       </c>
       <c r="J176" s="40"/>
       <c r="K176" s="63">
-        <f>D176*25</f>
+        <f t="shared" si="11"/>
         <v>11.774999999999999</v>
       </c>
       <c r="L176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>10.615711252653929</v>
       </c>
       <c r="M176">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.7749999999999995</v>
       </c>
       <c r="N176" s="3" t="s">
@@ -22351,15 +22309,15 @@
       </c>
       <c r="J177" s="40"/>
       <c r="K177" s="63">
-        <f>D177*25</f>
+        <f t="shared" si="11"/>
         <v>22.03</v>
       </c>
       <c r="L177">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.6740807989105768</v>
       </c>
       <c r="M177">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>17.03</v>
       </c>
       <c r="N177" s="3" t="s">
@@ -22395,15 +22353,15 @@
       </c>
       <c r="J178" s="13"/>
       <c r="K178" s="63">
-        <f>D178*25</f>
+        <f t="shared" si="11"/>
         <v>27.750000000000004</v>
       </c>
       <c r="L178">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.5045045045045038</v>
       </c>
       <c r="M178">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>22.750000000000004</v>
       </c>
       <c r="N178" s="3" t="s">
@@ -22439,15 +22397,15 @@
       </c>
       <c r="J179" s="13"/>
       <c r="K179" s="63">
-        <f>D179*25</f>
+        <f t="shared" si="11"/>
         <v>11.824999999999999</v>
       </c>
       <c r="L179">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>10.570824524312897</v>
       </c>
       <c r="M179">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.8249999999999993</v>
       </c>
       <c r="N179" s="3" t="s">
@@ -22481,15 +22439,15 @@
       </c>
       <c r="J180" s="40"/>
       <c r="K180" s="63">
-        <f>D180*25</f>
+        <f t="shared" si="11"/>
         <v>37.25</v>
       </c>
       <c r="L180">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.3557046979865772</v>
       </c>
       <c r="M180">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>32.25</v>
       </c>
       <c r="N180" s="3" t="s">
@@ -22523,15 +22481,15 @@
       </c>
       <c r="J181" s="40"/>
       <c r="K181" s="63">
-        <f>D181*25</f>
+        <f t="shared" si="11"/>
         <v>23.849999999999998</v>
       </c>
       <c r="L181">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.2410901467505244</v>
       </c>
       <c r="M181">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>18.850000000000001</v>
       </c>
       <c r="N181" s="3" t="s">
@@ -22565,15 +22523,15 @@
       </c>
       <c r="J182" s="40"/>
       <c r="K182" s="63">
-        <f>D182*25</f>
+        <f t="shared" si="11"/>
         <v>9.1750000000000007</v>
       </c>
       <c r="L182">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>13.623978201634877</v>
       </c>
       <c r="M182">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>4.1749999999999998</v>
       </c>
       <c r="N182" s="3" t="s">
@@ -22607,15 +22565,15 @@
       </c>
       <c r="J183" s="40"/>
       <c r="K183" s="63">
-        <f>D183*25</f>
+        <f t="shared" si="11"/>
         <v>23.7</v>
       </c>
       <c r="L183">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.2742616033755274</v>
       </c>
       <c r="M183">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>18.7</v>
       </c>
       <c r="N183" s="3" t="s">
@@ -22651,15 +22609,15 @@
       </c>
       <c r="J184" s="40"/>
       <c r="K184" s="63">
-        <f>D184*25</f>
+        <f t="shared" si="11"/>
         <v>18.475000000000001</v>
       </c>
       <c r="L184">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>6.7658998646820026</v>
       </c>
       <c r="M184">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>13.475000000000001</v>
       </c>
       <c r="N184" s="3" t="s">
@@ -22695,15 +22653,15 @@
       </c>
       <c r="J185" s="40"/>
       <c r="K185" s="63">
-        <f>D185*25</f>
+        <f t="shared" si="11"/>
         <v>25.25</v>
       </c>
       <c r="L185">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.9504950495049505</v>
       </c>
       <c r="M185">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>20.25</v>
       </c>
       <c r="N185" s="3" t="s">
@@ -22739,15 +22697,15 @@
       </c>
       <c r="J186" s="13"/>
       <c r="K186" s="63">
-        <f>D186*25</f>
+        <f t="shared" si="11"/>
         <v>31.75</v>
       </c>
       <c r="L186">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.9370078740157481</v>
       </c>
       <c r="M186">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>26.75</v>
       </c>
       <c r="N186" s="3" t="s">
@@ -22783,15 +22741,15 @@
       </c>
       <c r="J187" s="13"/>
       <c r="K187" s="63">
-        <f>D187*25</f>
+        <f t="shared" si="11"/>
         <v>16.875</v>
       </c>
       <c r="L187">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.4074074074074066</v>
       </c>
       <c r="M187">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>11.875000000000002</v>
       </c>
       <c r="N187" s="3" t="s">
@@ -22827,15 +22785,15 @@
       </c>
       <c r="J188" s="33"/>
       <c r="K188" s="63">
-        <f>D188*25</f>
+        <f t="shared" si="11"/>
         <v>13.775</v>
       </c>
       <c r="L188">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>9.0744101633393814</v>
       </c>
       <c r="M188">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>8.7750000000000021</v>
       </c>
       <c r="N188" s="3" t="s">
@@ -22873,15 +22831,15 @@
       </c>
       <c r="J189" s="13"/>
       <c r="K189" s="63">
-        <f>D189*25</f>
+        <f t="shared" si="11"/>
         <v>160</v>
       </c>
       <c r="L189">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.78125</v>
       </c>
       <c r="M189">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>155</v>
       </c>
       <c r="N189" s="3" t="s">
@@ -22917,15 +22875,15 @@
       </c>
       <c r="J190" s="13"/>
       <c r="K190" s="63">
-        <f>D190*25</f>
+        <f t="shared" si="11"/>
         <v>130</v>
       </c>
       <c r="L190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="M190">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>125.00000000000001</v>
       </c>
       <c r="N190" s="3" t="s">
@@ -22940,7 +22898,7 @@
       <c r="B191" s="25" t="s">
         <v>444</v>
       </c>
-      <c r="C191" s="108" t="s">
+      <c r="C191" s="13" t="s">
         <v>445</v>
       </c>
       <c r="D191" s="11">
@@ -22961,15 +22919,15 @@
       </c>
       <c r="J191" s="40"/>
       <c r="K191" s="63">
-        <f>D191*25</f>
+        <f t="shared" si="11"/>
         <v>6.9</v>
       </c>
       <c r="L191">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="M191">
-        <f t="shared" ref="M191:M195" si="6">(25-L191)*D191</f>
+        <f t="shared" ref="M191:M195" si="12">(25-L191)*D191</f>
         <v>1.9320000000000002</v>
       </c>
       <c r="N191" s="63" t="s">
@@ -23005,15 +22963,15 @@
       </c>
       <c r="J192" s="55"/>
       <c r="K192" s="63">
-        <f>D192*25</f>
+        <f t="shared" si="11"/>
         <v>14.899999999999999</v>
       </c>
       <c r="L192">
-        <f t="shared" ref="L192:L195" si="7">IF(5/D192&gt;18,18,5/D192)</f>
+        <f t="shared" ref="L192:L195" si="13">IF(5/D192&gt;18,18,5/D192)</f>
         <v>8.3892617449664435</v>
       </c>
       <c r="M192">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>9.8999999999999986</v>
       </c>
       <c r="N192" s="3" t="s">
@@ -23028,7 +22986,7 @@
       <c r="B193" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="C193" s="106" t="s">
+      <c r="C193" s="11" t="s">
         <v>449</v>
       </c>
       <c r="D193" s="11">
@@ -23049,15 +23007,15 @@
       </c>
       <c r="J193" s="13"/>
       <c r="K193" s="63">
-        <f>D193*25</f>
+        <f t="shared" si="11"/>
         <v>6.05</v>
       </c>
       <c r="L193">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="M193">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1.694</v>
       </c>
       <c r="N193" s="63" t="s">
@@ -23093,15 +23051,15 @@
       </c>
       <c r="J194" s="40"/>
       <c r="K194" s="63">
-        <f>D194*25</f>
+        <f t="shared" si="11"/>
         <v>14.324999999999999</v>
       </c>
       <c r="L194">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>8.7260034904013963</v>
       </c>
       <c r="M194">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>9.3249999999999993</v>
       </c>
       <c r="N194" s="3" t="s">
@@ -23137,15 +23095,15 @@
       </c>
       <c r="J195" s="40"/>
       <c r="K195" s="63">
-        <f>D195*25</f>
+        <f t="shared" si="11"/>
         <v>18.824999999999999</v>
       </c>
       <c r="L195">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>6.6401062416998675</v>
       </c>
       <c r="M195">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>13.824999999999999</v>
       </c>
       <c r="N195" s="3" t="s">
@@ -23157,27 +23115,27 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O195" xr:uid="{27E63DE1-C4C6-4AA3-B6A8-1931E3CE8F5B}"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K2:K195">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
       <formula>8.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:M1 O1 K1:K1048576">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+      <formula>3.3</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M195">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
       <formula>2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
-      <formula>3.3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23251,11 +23209,11 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C48" si="0">VLOOKUP(A3,$H$2:$I$200,2,0)</f>
+        <f t="shared" ref="C3:C36" si="0">VLOOKUP(A3,$H$2:$I$200,2,0)</f>
         <v>4.2</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D48" si="1">C3-B3</f>
+        <f t="shared" ref="D3:D36" si="1">C3-B3</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="E3">
@@ -24101,11 +24059,11 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <f>VLOOKUP(A37,$H$2:$I$200,2,0)</f>
+        <f t="shared" ref="C37:C47" si="2">VLOOKUP(A37,$H$2:$I$200,2,0)</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="D37">
-        <f>C37-B37</f>
+        <f t="shared" ref="D37:D47" si="3">C37-B37</f>
         <v>2.5999999999999996</v>
       </c>
       <c r="E37">
@@ -24126,11 +24084,11 @@
         <v>2</v>
       </c>
       <c r="C38">
-        <f>VLOOKUP(A38,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>3.7</v>
       </c>
       <c r="D38">
-        <f>C38-B38</f>
+        <f t="shared" si="3"/>
         <v>1.7000000000000002</v>
       </c>
       <c r="E38">
@@ -24151,11 +24109,11 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <f>VLOOKUP(A39,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
       <c r="D39">
-        <f>C39-B39</f>
+        <f t="shared" si="3"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="E39">
@@ -24176,11 +24134,11 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <f>VLOOKUP(A40,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>5.5</v>
       </c>
       <c r="D40">
-        <f>C40-B40</f>
+        <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
       <c r="E40">
@@ -24201,11 +24159,11 @@
         <v>2</v>
       </c>
       <c r="C41">
-        <f>VLOOKUP(A41,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>4.8</v>
       </c>
       <c r="D41">
-        <f>C41-B41</f>
+        <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
       <c r="E41">
@@ -24226,11 +24184,11 @@
         <v>2</v>
       </c>
       <c r="C42">
-        <f>VLOOKUP(A42,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="D42">
-        <f>C42-B42</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="E42">
@@ -24251,11 +24209,11 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <f>VLOOKUP(A43,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>4.5</v>
       </c>
       <c r="D43">
-        <f>C43-B43</f>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="E43">
@@ -24276,11 +24234,11 @@
         <v>1.7</v>
       </c>
       <c r="C44">
-        <f>VLOOKUP(A44,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>3.7</v>
       </c>
       <c r="D44">
-        <f>C44-B44</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="E44">
@@ -24301,11 +24259,11 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <f>VLOOKUP(A45,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D45">
-        <f>C45-B45</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E45">
@@ -24326,11 +24284,11 @@
         <v>1.8</v>
       </c>
       <c r="C46">
-        <f>VLOOKUP(A46,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>4.8</v>
       </c>
       <c r="D46">
-        <f>C46-B46</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E46">
@@ -24351,11 +24309,11 @@
         <v>1.8</v>
       </c>
       <c r="C47">
-        <f>VLOOKUP(A47,$H$2:$I$200,2,0)</f>
+        <f t="shared" si="2"/>
         <v>4.8</v>
       </c>
       <c r="D47">
-        <f>C47-B47</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E47">
@@ -25453,15 +25411,15 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A49:A1048429 A1:A47">
+    <cfRule type="duplicateValues" dxfId="2" priority="39"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:A1048429 A1:A47">
-    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D49:D1048576 D1:D47">
+  <conditionalFormatting sqref="D1:D47 D49:D1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
